--- a/data/processed/academic_calendar_2426.xlsx
+++ b/data/processed/academic_calendar_2426.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30305"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AC535C9-4676-4F8E-90E7-62989DD2F464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F85DD7C5-092E-425B-9653-CA9015DE0EEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="44">
   <si>
     <t>Date</t>
   </si>
@@ -155,6 +155,15 @@
   <si>
     <t>paper_showing</t>
   </si>
+  <si>
+    <t>id-e-milad</t>
+  </si>
+  <si>
+    <t>dussehra</t>
+  </si>
+  <si>
+    <t>valmiki jayanti</t>
+  </si>
 </sst>
 </file>
 
@@ -202,12 +211,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -426,14 +438,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C883"/>
+  <dimension ref="A1:E1036"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="33" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" ht="12.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -441,7 +453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" ht="12.75">
       <c r="A2" s="2">
         <v>45292</v>
       </c>
@@ -449,7 +461,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" ht="12.75">
       <c r="A3" s="2">
         <v>45293</v>
       </c>
@@ -457,7 +469,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" ht="12.75">
       <c r="A4" s="2">
         <v>45294</v>
       </c>
@@ -465,7 +477,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" ht="12.75">
       <c r="A5" s="2">
         <v>45295</v>
       </c>
@@ -473,7 +485,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" ht="12.75">
       <c r="A6" s="2">
         <v>45296</v>
       </c>
@@ -481,7 +493,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" ht="12.75">
       <c r="A7" s="2">
         <v>45297</v>
       </c>
@@ -489,7 +501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" ht="12.75">
       <c r="A8" s="2">
         <v>45298</v>
       </c>
@@ -497,7 +509,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" ht="12.75">
       <c r="A9" s="2">
         <v>45299</v>
       </c>
@@ -508,7 +520,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" ht="12.75">
       <c r="A10" s="2">
         <v>45300</v>
       </c>
@@ -516,7 +528,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" ht="12.75">
       <c r="A11" s="2">
         <v>45301</v>
       </c>
@@ -524,7 +536,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" ht="12.75">
       <c r="A12" s="2">
         <v>45302</v>
       </c>
@@ -532,7 +544,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" ht="12.75">
       <c r="A13" s="2">
         <v>45303</v>
       </c>
@@ -540,7 +552,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" ht="12.75">
       <c r="A14" s="2">
         <v>45304</v>
       </c>
@@ -548,7 +560,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" ht="12.75">
       <c r="A15" s="2">
         <v>45305</v>
       </c>
@@ -556,7 +568,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" ht="12.75">
       <c r="A16" s="2">
         <v>45306</v>
       </c>
@@ -564,7 +576,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" ht="12.75">
       <c r="A17" s="2">
         <v>45307</v>
       </c>
@@ -572,7 +584,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" ht="12.75">
       <c r="A18" s="2">
         <v>45308</v>
       </c>
@@ -580,7 +592,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" ht="12.75">
       <c r="A19" s="2">
         <v>45309</v>
       </c>
@@ -588,7 +600,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" ht="12.75">
       <c r="A20" s="2">
         <v>45310</v>
       </c>
@@ -599,7 +611,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" ht="12.75">
       <c r="A21" s="2">
         <v>45311</v>
       </c>
@@ -610,7 +622,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" ht="12.75">
       <c r="A22" s="2">
         <v>45312</v>
       </c>
@@ -618,7 +630,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" ht="12.75">
       <c r="A23" s="2">
         <v>45313</v>
       </c>
@@ -626,7 +638,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" ht="12.75">
       <c r="A24" s="2">
         <v>45314</v>
       </c>
@@ -634,7 +646,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" ht="12.75">
       <c r="A25" s="2">
         <v>45315</v>
       </c>
@@ -642,7 +654,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" ht="12.75">
       <c r="A26" s="2">
         <v>45316</v>
       </c>
@@ -650,7 +662,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" ht="12.75">
       <c r="A27" s="2">
         <v>45317</v>
       </c>
@@ -658,7 +670,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" ht="12.75">
       <c r="A28" s="2">
         <v>45318</v>
       </c>
@@ -666,7 +678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" ht="12.75">
       <c r="A29" s="2">
         <v>45319</v>
       </c>
@@ -674,7 +686,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" ht="12.75">
       <c r="A30" s="2">
         <v>45320</v>
       </c>
@@ -682,7 +694,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" ht="12.75">
       <c r="A31" s="2">
         <v>45321</v>
       </c>
@@ -690,7 +702,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" ht="12.75">
       <c r="A32" s="2">
         <v>45322</v>
       </c>
@@ -698,7 +710,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" ht="12.75">
       <c r="A33" s="2">
         <v>45323</v>
       </c>
@@ -706,7 +718,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" ht="12.75">
       <c r="A34" s="2">
         <v>45324</v>
       </c>
@@ -714,7 +726,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" ht="12.75">
       <c r="A35" s="2">
         <v>45325</v>
       </c>
@@ -722,7 +734,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" ht="12.75">
       <c r="A36" s="2">
         <v>45326</v>
       </c>
@@ -730,7 +742,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" ht="12.75">
       <c r="A37" s="2">
         <v>45327</v>
       </c>
@@ -738,7 +750,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" ht="12.75">
       <c r="A38" s="2">
         <v>45328</v>
       </c>
@@ -746,7 +758,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" ht="12.75">
       <c r="A39" s="2">
         <v>45329</v>
       </c>
@@ -754,7 +766,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" ht="12.75">
       <c r="A40" s="2">
         <v>45330</v>
       </c>
@@ -762,7 +774,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" ht="12.75">
       <c r="A41" s="2">
         <v>45331</v>
       </c>
@@ -770,7 +782,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" ht="12.75">
       <c r="A42" s="2">
         <v>45332</v>
       </c>
@@ -778,7 +790,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" ht="12.75">
       <c r="A43" s="2">
         <v>45333</v>
       </c>
@@ -786,7 +798,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" ht="12.75">
       <c r="A44" s="2">
         <v>45334</v>
       </c>
@@ -794,7 +806,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" ht="12.75">
       <c r="A45" s="2">
         <v>45335</v>
       </c>
@@ -802,7 +814,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" ht="12.75">
       <c r="A46" s="2">
         <v>45336</v>
       </c>
@@ -810,7 +822,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" ht="12.75">
       <c r="A47" s="2">
         <v>45337</v>
       </c>
@@ -818,7 +830,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" ht="12.75">
       <c r="A48" s="2">
         <v>45338</v>
       </c>
@@ -826,7 +838,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" ht="12.75">
       <c r="A49" s="2">
         <v>45339</v>
       </c>
@@ -834,7 +846,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" ht="12.75">
       <c r="A50" s="2">
         <v>45340</v>
       </c>
@@ -842,7 +854,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" ht="12.75">
       <c r="A51" s="2">
         <v>45341</v>
       </c>
@@ -850,7 +862,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" ht="12.75">
       <c r="A52" s="2">
         <v>45342</v>
       </c>
@@ -858,7 +870,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" ht="12.75">
       <c r="A53" s="2">
         <v>45343</v>
       </c>
@@ -866,7 +878,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" ht="12.75">
       <c r="A54" s="2">
         <v>45344</v>
       </c>
@@ -874,7 +886,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" ht="12.75">
       <c r="A55" s="2">
         <v>45345</v>
       </c>
@@ -882,7 +894,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" ht="12.75">
       <c r="A56" s="2">
         <v>45346</v>
       </c>
@@ -890,7 +902,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" ht="12.75">
       <c r="A57" s="2">
         <v>45347</v>
       </c>
@@ -898,7 +910,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" ht="12.75">
       <c r="A58" s="2">
         <v>45348</v>
       </c>
@@ -906,7 +918,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" ht="12.75">
       <c r="A59" s="2">
         <v>45349</v>
       </c>
@@ -914,7 +926,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" ht="12.75">
       <c r="A60" s="2">
         <v>45350</v>
       </c>
@@ -922,7 +934,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" ht="12.75">
       <c r="A61" s="2">
         <v>45351</v>
       </c>
@@ -930,7 +942,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" ht="12.75">
       <c r="A62" s="2">
         <v>45352</v>
       </c>
@@ -938,7 +950,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" ht="12.75">
       <c r="A63" s="2">
         <v>45353</v>
       </c>
@@ -946,7 +958,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" ht="12.75">
       <c r="A64" s="2">
         <v>45354</v>
       </c>
@@ -954,7 +966,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" ht="12.75">
       <c r="A65" s="2">
         <v>45355</v>
       </c>
@@ -962,7 +974,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" ht="12.75">
       <c r="A66" s="2">
         <v>45356</v>
       </c>
@@ -970,7 +982,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" ht="12.75">
       <c r="A67" s="2">
         <v>45357</v>
       </c>
@@ -978,7 +990,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" ht="12.75">
       <c r="A68" s="2">
         <v>45358</v>
       </c>
@@ -986,7 +998,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" ht="12.75">
       <c r="A69" s="2">
         <v>45359</v>
       </c>
@@ -994,7 +1006,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" ht="12.75">
       <c r="A70" s="2">
         <v>45360</v>
       </c>
@@ -1002,7 +1014,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" ht="12.75">
       <c r="A71" s="2">
         <v>45361</v>
       </c>
@@ -1010,7 +1022,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" ht="12.75">
       <c r="A72" s="2">
         <v>45362</v>
       </c>
@@ -1018,7 +1030,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" ht="12.75">
       <c r="A73" s="2">
         <v>45363</v>
       </c>
@@ -1026,7 +1038,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" ht="12.75">
       <c r="A74" s="2">
         <v>45364</v>
       </c>
@@ -1034,7 +1046,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" ht="12.75">
       <c r="A75" s="2">
         <v>45365</v>
       </c>
@@ -1042,7 +1054,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" ht="12.75">
       <c r="A76" s="2">
         <v>45366</v>
       </c>
@@ -1053,7 +1065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" ht="12.75">
       <c r="A77" s="2">
         <v>45367</v>
       </c>
@@ -1064,7 +1076,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" ht="12.75">
       <c r="A78" s="2">
         <v>45368</v>
       </c>
@@ -1072,7 +1084,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" ht="12.75">
       <c r="A79" s="2">
         <v>45369</v>
       </c>
@@ -1080,7 +1092,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" ht="12.75">
       <c r="A80" s="2">
         <v>45370</v>
       </c>
@@ -1088,7 +1100,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" ht="12.75">
       <c r="A81" s="2">
         <v>45371</v>
       </c>
@@ -1096,7 +1108,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" ht="12.75">
       <c r="A82" s="2">
         <v>45372</v>
       </c>
@@ -1104,7 +1116,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" ht="12.75">
       <c r="A83" s="2">
         <v>45373</v>
       </c>
@@ -1115,7 +1127,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" ht="12.75">
       <c r="A84" s="2">
         <v>45374</v>
       </c>
@@ -1126,7 +1138,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" ht="12.75">
       <c r="A85" s="2">
         <v>45375</v>
       </c>
@@ -1134,7 +1146,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" ht="12.75">
       <c r="A86" s="2">
         <v>45376</v>
       </c>
@@ -1145,7 +1157,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" ht="12.75">
       <c r="A87" s="2">
         <v>45377</v>
       </c>
@@ -1153,7 +1165,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" ht="12.75">
       <c r="A88" s="2">
         <v>45378</v>
       </c>
@@ -1161,7 +1173,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" ht="12.75">
       <c r="A89" s="2">
         <v>45379</v>
       </c>
@@ -1169,7 +1181,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" ht="12.75">
       <c r="A90" s="2">
         <v>45380</v>
       </c>
@@ -1180,7 +1192,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" ht="12.75">
       <c r="A91" s="2">
         <v>45381</v>
       </c>
@@ -1188,7 +1200,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" ht="12.75">
       <c r="A92" s="2">
         <v>45382</v>
       </c>
@@ -1196,7 +1208,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" ht="12.75">
       <c r="A93" s="2">
         <v>45383</v>
       </c>
@@ -1204,7 +1216,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" ht="12.75">
       <c r="A94" s="2">
         <v>45384</v>
       </c>
@@ -1212,7 +1224,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" ht="12.75">
       <c r="A95" s="2">
         <v>45385</v>
       </c>
@@ -1220,7 +1232,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" ht="12.75">
       <c r="A96" s="2">
         <v>45386</v>
       </c>
@@ -1228,7 +1240,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" ht="12.75">
       <c r="A97" s="2">
         <v>45387</v>
       </c>
@@ -1236,7 +1248,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:3" ht="12.75">
       <c r="A98" s="2">
         <v>45388</v>
       </c>
@@ -1244,7 +1256,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" ht="12.75">
       <c r="A99" s="2">
         <v>45389</v>
       </c>
@@ -1252,7 +1264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:3" ht="12.75">
       <c r="A100" s="2">
         <v>45390</v>
       </c>
@@ -1260,7 +1272,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" ht="12.75">
       <c r="A101" s="2">
         <v>45391</v>
       </c>
@@ -1268,7 +1280,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:3" ht="12.75">
       <c r="A102" s="2">
         <v>45392</v>
       </c>
@@ -1276,7 +1288,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:3">
+    <row r="103" spans="1:3" ht="12.75">
       <c r="A103" s="2">
         <v>45393</v>
       </c>
@@ -1287,7 +1299,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="104" spans="1:3">
+    <row r="104" spans="1:3" ht="12.75">
       <c r="A104" s="2">
         <v>45394</v>
       </c>
@@ -1295,7 +1307,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:3">
+    <row r="105" spans="1:3" ht="12.75">
       <c r="A105" s="2">
         <v>45395</v>
       </c>
@@ -1303,7 +1315,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:3">
+    <row r="106" spans="1:3" ht="12.75">
       <c r="A106" s="2">
         <v>45396</v>
       </c>
@@ -1311,7 +1323,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:3">
+    <row r="107" spans="1:3" ht="12.75">
       <c r="A107" s="2">
         <v>45397</v>
       </c>
@@ -1319,7 +1331,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:3">
+    <row r="108" spans="1:3" ht="12.75">
       <c r="A108" s="2">
         <v>45398</v>
       </c>
@@ -1327,7 +1339,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
+    <row r="109" spans="1:3" ht="12.75">
       <c r="A109" s="2">
         <v>45399</v>
       </c>
@@ -1338,7 +1350,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="110" spans="1:3">
+    <row r="110" spans="1:3" ht="12.75">
       <c r="A110" s="2">
         <v>45400</v>
       </c>
@@ -1346,7 +1358,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="1:3">
+    <row r="111" spans="1:3" ht="12.75">
       <c r="A111" s="2">
         <v>45401</v>
       </c>
@@ -1354,7 +1366,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:3">
+    <row r="112" spans="1:3" ht="12.75">
       <c r="A112" s="2">
         <v>45402</v>
       </c>
@@ -1362,7 +1374,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:3">
+    <row r="113" spans="1:3" ht="12.75">
       <c r="A113" s="2">
         <v>45403</v>
       </c>
@@ -1370,7 +1382,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
+    <row r="114" spans="1:3" ht="12.75">
       <c r="A114" s="2">
         <v>45404</v>
       </c>
@@ -1378,7 +1390,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
+    <row r="115" spans="1:3" ht="12.75">
       <c r="A115" s="2">
         <v>45405</v>
       </c>
@@ -1386,7 +1398,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
+    <row r="116" spans="1:3" ht="12.75">
       <c r="A116" s="2">
         <v>45406</v>
       </c>
@@ -1394,7 +1406,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
+    <row r="117" spans="1:3" ht="12.75">
       <c r="A117" s="2">
         <v>45407</v>
       </c>
@@ -1402,7 +1414,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
+    <row r="118" spans="1:3" ht="12.75">
       <c r="A118" s="2">
         <v>45408</v>
       </c>
@@ -1410,7 +1422,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
+    <row r="119" spans="1:3" ht="12.75">
       <c r="A119" s="2">
         <v>45409</v>
       </c>
@@ -1418,7 +1430,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
+    <row r="120" spans="1:3" ht="12.75">
       <c r="A120" s="2">
         <v>45410</v>
       </c>
@@ -1426,7 +1438,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
+    <row r="121" spans="1:3" ht="12.75">
       <c r="A121" s="2">
         <v>45411</v>
       </c>
@@ -1434,7 +1446,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
+    <row r="122" spans="1:3" ht="12.75">
       <c r="A122" s="2">
         <v>45412</v>
       </c>
@@ -1445,7 +1457,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
+    <row r="123" spans="1:3" ht="12.75">
       <c r="A123" s="2">
         <v>45413</v>
       </c>
@@ -1453,7 +1465,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
+    <row r="124" spans="1:3" ht="12.75">
       <c r="A124" s="2">
         <v>45414</v>
       </c>
@@ -1461,7 +1473,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
+    <row r="125" spans="1:3" ht="12.75">
       <c r="A125" s="2">
         <v>45415</v>
       </c>
@@ -1469,7 +1481,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
+    <row r="126" spans="1:3" ht="12.75">
       <c r="A126" s="2">
         <v>45416</v>
       </c>
@@ -1477,7 +1489,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
+    <row r="127" spans="1:3" ht="12.75">
       <c r="A127" s="2">
         <v>45417</v>
       </c>
@@ -1485,7 +1497,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="128" spans="1:3">
+    <row r="128" spans="1:3" ht="12.75">
       <c r="A128" s="2">
         <v>45418</v>
       </c>
@@ -1493,7 +1505,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="129" spans="1:2">
+    <row r="129" spans="1:2" ht="12.75">
       <c r="A129" s="2">
         <v>45419</v>
       </c>
@@ -1501,7 +1513,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="130" spans="1:2">
+    <row r="130" spans="1:2" ht="12.75">
       <c r="A130" s="2">
         <v>45420</v>
       </c>
@@ -1509,7 +1521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="131" spans="1:2">
+    <row r="131" spans="1:2" ht="12.75">
       <c r="A131" s="2">
         <v>45421</v>
       </c>
@@ -1517,7 +1529,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="132" spans="1:2">
+    <row r="132" spans="1:2" ht="12.75">
       <c r="A132" s="2">
         <v>45422</v>
       </c>
@@ -1525,7 +1537,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="133" spans="1:2">
+    <row r="133" spans="1:2" ht="12.75">
       <c r="A133" s="2">
         <v>45423</v>
       </c>
@@ -1533,7 +1545,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="134" spans="1:2">
+    <row r="134" spans="1:2" ht="12.75">
       <c r="A134" s="2">
         <v>45424</v>
       </c>
@@ -1541,7 +1553,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="135" spans="1:2">
+    <row r="135" spans="1:2" ht="12.75">
       <c r="A135" s="2">
         <v>45425</v>
       </c>
@@ -1549,7 +1561,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:2">
+    <row r="136" spans="1:2" ht="12.75">
       <c r="A136" s="2">
         <v>45426</v>
       </c>
@@ -1557,7 +1569,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:2">
+    <row r="137" spans="1:2" ht="12.75">
       <c r="A137" s="2">
         <v>45427</v>
       </c>
@@ -1565,7 +1577,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="1:2">
+    <row r="138" spans="1:2" ht="12.75">
       <c r="A138" s="2">
         <v>45428</v>
       </c>
@@ -1573,7 +1585,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="1:2">
+    <row r="139" spans="1:2" ht="12.75">
       <c r="A139" s="2">
         <v>45429</v>
       </c>
@@ -1581,7 +1593,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:2">
+    <row r="140" spans="1:2" ht="12.75">
       <c r="A140" s="2">
         <v>45430</v>
       </c>
@@ -1589,7 +1601,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="141" spans="1:2">
+    <row r="141" spans="1:2" ht="12.75">
       <c r="A141" s="2">
         <v>45431</v>
       </c>
@@ -1597,7 +1609,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="142" spans="1:2">
+    <row r="142" spans="1:2" ht="12.75">
       <c r="A142" s="2">
         <v>45432</v>
       </c>
@@ -1605,7 +1617,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="143" spans="1:2">
+    <row r="143" spans="1:2" ht="12.75">
       <c r="A143" s="2">
         <v>45433</v>
       </c>
@@ -1613,7 +1625,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:2">
+    <row r="144" spans="1:2" ht="12.75">
       <c r="A144" s="2">
         <v>45434</v>
       </c>
@@ -1621,7 +1633,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="145" spans="1:2">
+    <row r="145" spans="1:2" ht="12.75">
       <c r="A145" s="2">
         <v>45435</v>
       </c>
@@ -1629,7 +1641,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="146" spans="1:2">
+    <row r="146" spans="1:2" ht="12.75">
       <c r="A146" s="2">
         <v>45436</v>
       </c>
@@ -1637,7 +1649,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="147" spans="1:2">
+    <row r="147" spans="1:2" ht="12.75">
       <c r="A147" s="2">
         <v>45437</v>
       </c>
@@ -1645,7 +1657,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="148" spans="1:2">
+    <row r="148" spans="1:2" ht="12.75">
       <c r="A148" s="2">
         <v>45438</v>
       </c>
@@ -1653,7 +1665,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="149" spans="1:2">
+    <row r="149" spans="1:2" ht="12.75">
       <c r="A149" s="2">
         <v>45439</v>
       </c>
@@ -1661,7 +1673,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="150" spans="1:2">
+    <row r="150" spans="1:2" ht="12.75">
       <c r="A150" s="2">
         <v>45440</v>
       </c>
@@ -1669,7 +1681,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="151" spans="1:2">
+    <row r="151" spans="1:2" ht="12.75">
       <c r="A151" s="2">
         <v>45441</v>
       </c>
@@ -1677,7 +1689,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="152" spans="1:2">
+    <row r="152" spans="1:2" ht="12.75">
       <c r="A152" s="2">
         <v>45442</v>
       </c>
@@ -1685,7 +1697,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="153" spans="1:2">
+    <row r="153" spans="1:2" ht="12.75">
       <c r="A153" s="2">
         <v>45443</v>
       </c>
@@ -1693,7 +1705,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="154" spans="1:2">
+    <row r="154" spans="1:2" ht="12.75">
       <c r="A154" s="2">
         <v>45444</v>
       </c>
@@ -1701,7 +1713,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="155" spans="1:2">
+    <row r="155" spans="1:2" ht="12.75">
       <c r="A155" s="2">
         <v>45445</v>
       </c>
@@ -1709,7 +1721,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="156" spans="1:2">
+    <row r="156" spans="1:2" ht="12.75">
       <c r="A156" s="2">
         <v>45446</v>
       </c>
@@ -1717,7 +1729,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="157" spans="1:2">
+    <row r="157" spans="1:2" ht="12.75">
       <c r="A157" s="2">
         <v>45447</v>
       </c>
@@ -1725,7 +1737,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="158" spans="1:2">
+    <row r="158" spans="1:2" ht="12.75">
       <c r="A158" s="2">
         <v>45448</v>
       </c>
@@ -1733,7 +1745,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="159" spans="1:2">
+    <row r="159" spans="1:2" ht="12.75">
       <c r="A159" s="2">
         <v>45449</v>
       </c>
@@ -1741,7 +1753,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="160" spans="1:2">
+    <row r="160" spans="1:2" ht="12.75">
       <c r="A160" s="2">
         <v>45450</v>
       </c>
@@ -1749,7 +1761,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="161" spans="1:2">
+    <row r="161" spans="1:2" ht="12.75">
       <c r="A161" s="2">
         <v>45451</v>
       </c>
@@ -1757,7 +1769,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="162" spans="1:2">
+    <row r="162" spans="1:2" ht="12.75">
       <c r="A162" s="2">
         <v>45452</v>
       </c>
@@ -1765,7 +1777,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="163" spans="1:2">
+    <row r="163" spans="1:2" ht="12.75">
       <c r="A163" s="2">
         <v>45453</v>
       </c>
@@ -1773,7 +1785,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="164" spans="1:2">
+    <row r="164" spans="1:2" ht="12.75">
       <c r="A164" s="2">
         <v>45454</v>
       </c>
@@ -1781,7 +1793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="165" spans="1:2">
+    <row r="165" spans="1:2" ht="12.75">
       <c r="A165" s="2">
         <v>45455</v>
       </c>
@@ -1789,7 +1801,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="166" spans="1:2">
+    <row r="166" spans="1:2" ht="12.75">
       <c r="A166" s="2">
         <v>45456</v>
       </c>
@@ -1797,7 +1809,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="167" spans="1:2">
+    <row r="167" spans="1:2" ht="12.75">
       <c r="A167" s="2">
         <v>45457</v>
       </c>
@@ -1805,7 +1817,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="168" spans="1:2">
+    <row r="168" spans="1:2" ht="12.75">
       <c r="A168" s="2">
         <v>45458</v>
       </c>
@@ -1813,7 +1825,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="169" spans="1:2">
+    <row r="169" spans="1:2" ht="12.75">
       <c r="A169" s="2">
         <v>45459</v>
       </c>
@@ -1821,7 +1833,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="170" spans="1:2">
+    <row r="170" spans="1:2" ht="12.75">
       <c r="A170" s="2">
         <v>45460</v>
       </c>
@@ -1829,7 +1841,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="171" spans="1:2">
+    <row r="171" spans="1:2" ht="12.75">
       <c r="A171" s="2">
         <v>45461</v>
       </c>
@@ -1837,7 +1849,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="172" spans="1:2">
+    <row r="172" spans="1:2" ht="12.75">
       <c r="A172" s="2">
         <v>45462</v>
       </c>
@@ -1845,7 +1857,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="173" spans="1:2">
+    <row r="173" spans="1:2" ht="12.75">
       <c r="A173" s="2">
         <v>45463</v>
       </c>
@@ -1853,7 +1865,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="174" spans="1:2">
+    <row r="174" spans="1:2" ht="12.75">
       <c r="A174" s="2">
         <v>45464</v>
       </c>
@@ -1861,7 +1873,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="175" spans="1:2">
+    <row r="175" spans="1:2" ht="12.75">
       <c r="A175" s="2">
         <v>45465</v>
       </c>
@@ -1869,7 +1881,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="176" spans="1:2">
+    <row r="176" spans="1:2" ht="12.75">
       <c r="A176" s="2">
         <v>45466</v>
       </c>
@@ -1877,7 +1889,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="177" spans="1:2">
+    <row r="177" spans="1:2" ht="12.75">
       <c r="A177" s="2">
         <v>45467</v>
       </c>
@@ -1885,7 +1897,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="178" spans="1:2">
+    <row r="178" spans="1:2" ht="12.75">
       <c r="A178" s="2">
         <v>45468</v>
       </c>
@@ -1893,7 +1905,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="179" spans="1:2">
+    <row r="179" spans="1:2" ht="12.75">
       <c r="A179" s="2">
         <v>45469</v>
       </c>
@@ -1901,7 +1913,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="180" spans="1:2">
+    <row r="180" spans="1:2" ht="12.75">
       <c r="A180" s="2">
         <v>45470</v>
       </c>
@@ -1909,7 +1921,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="181" spans="1:2">
+    <row r="181" spans="1:2" ht="12.75">
       <c r="A181" s="2">
         <v>45471</v>
       </c>
@@ -1917,7 +1929,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="182" spans="1:2">
+    <row r="182" spans="1:2" ht="12.75">
       <c r="A182" s="2">
         <v>45472</v>
       </c>
@@ -1925,7 +1937,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="183" spans="1:2">
+    <row r="183" spans="1:2" ht="12.75">
       <c r="A183" s="2">
         <v>45473</v>
       </c>
@@ -1933,7 +1945,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="184" spans="1:2">
+    <row r="184" spans="1:2" ht="12.75">
       <c r="A184" s="2">
         <v>45474</v>
       </c>
@@ -1941,7 +1953,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="185" spans="1:2">
+    <row r="185" spans="1:2" ht="12.75">
       <c r="A185" s="2">
         <v>45475</v>
       </c>
@@ -1949,7 +1961,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="186" spans="1:2">
+    <row r="186" spans="1:2" ht="12.75">
       <c r="A186" s="2">
         <v>45476</v>
       </c>
@@ -1957,7 +1969,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="187" spans="1:2">
+    <row r="187" spans="1:2" ht="12.75">
       <c r="A187" s="2">
         <v>45477</v>
       </c>
@@ -1965,7 +1977,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="188" spans="1:2">
+    <row r="188" spans="1:2" ht="12.75">
       <c r="A188" s="2">
         <v>45478</v>
       </c>
@@ -1973,7 +1985,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="189" spans="1:2">
+    <row r="189" spans="1:2" ht="12.75">
       <c r="A189" s="2">
         <v>45479</v>
       </c>
@@ -1981,7 +1993,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="190" spans="1:2">
+    <row r="190" spans="1:2" ht="12.75">
       <c r="A190" s="2">
         <v>45480</v>
       </c>
@@ -1989,7 +2001,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="191" spans="1:2">
+    <row r="191" spans="1:2" ht="12.75">
       <c r="A191" s="2">
         <v>45481</v>
       </c>
@@ -1997,7 +2009,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="192" spans="1:2">
+    <row r="192" spans="1:2" ht="12.75">
       <c r="A192" s="2">
         <v>45482</v>
       </c>
@@ -2005,7 +2017,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="193" spans="1:2">
+    <row r="193" spans="1:2" ht="12.75">
       <c r="A193" s="2">
         <v>45483</v>
       </c>
@@ -2013,7 +2025,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="194" spans="1:2">
+    <row r="194" spans="1:2" ht="12.75">
       <c r="A194" s="2">
         <v>45484</v>
       </c>
@@ -2021,7 +2033,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="195" spans="1:2">
+    <row r="195" spans="1:2" ht="12.75">
       <c r="A195" s="2">
         <v>45485</v>
       </c>
@@ -2029,7 +2041,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="196" spans="1:2">
+    <row r="196" spans="1:2" ht="12.75">
       <c r="A196" s="2">
         <v>45486</v>
       </c>
@@ -2037,7 +2049,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="197" spans="1:2">
+    <row r="197" spans="1:2" ht="12.75">
       <c r="A197" s="2">
         <v>45487</v>
       </c>
@@ -2045,7 +2057,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="198" spans="1:2">
+    <row r="198" spans="1:2" ht="12.75">
       <c r="A198" s="2">
         <v>45488</v>
       </c>
@@ -2053,7 +2065,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="199" spans="1:2">
+    <row r="199" spans="1:2" ht="12.75">
       <c r="A199" s="2">
         <v>45489</v>
       </c>
@@ -2061,7 +2073,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="200" spans="1:2">
+    <row r="200" spans="1:2" ht="12.75">
       <c r="A200" s="2">
         <v>45490</v>
       </c>
@@ -2069,7 +2081,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="201" spans="1:2">
+    <row r="201" spans="1:2" ht="12.75">
       <c r="A201" s="2">
         <v>45491</v>
       </c>
@@ -2077,7 +2089,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="202" spans="1:2">
+    <row r="202" spans="1:2" ht="12.75">
       <c r="A202" s="2">
         <v>45492</v>
       </c>
@@ -2085,7 +2097,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="203" spans="1:2">
+    <row r="203" spans="1:2" ht="12.75">
       <c r="A203" s="2">
         <v>45493</v>
       </c>
@@ -2093,7 +2105,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="204" spans="1:2">
+    <row r="204" spans="1:2" ht="12.75">
       <c r="A204" s="2">
         <v>45494</v>
       </c>
@@ -2101,7 +2113,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="205" spans="1:2">
+    <row r="205" spans="1:2" ht="12.75">
       <c r="A205" s="2">
         <v>45495</v>
       </c>
@@ -2109,7 +2121,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="206" spans="1:2">
+    <row r="206" spans="1:2" ht="12.75">
       <c r="A206" s="2">
         <v>45496</v>
       </c>
@@ -2117,7 +2129,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="207" spans="1:2">
+    <row r="207" spans="1:2" ht="12.75">
       <c r="A207" s="2">
         <v>45497</v>
       </c>
@@ -2125,7 +2137,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="208" spans="1:2">
+    <row r="208" spans="1:2" ht="12.75">
       <c r="A208" s="2">
         <v>45498</v>
       </c>
@@ -2133,7 +2145,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="209" spans="1:3">
+    <row r="209" spans="1:3" ht="12.75">
       <c r="A209" s="2">
         <v>45499</v>
       </c>
@@ -2141,7 +2153,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="210" spans="1:3">
+    <row r="210" spans="1:3" ht="12.75">
       <c r="A210" s="2">
         <v>45500</v>
       </c>
@@ -2149,7 +2161,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="211" spans="1:3">
+    <row r="211" spans="1:3" ht="12.75">
       <c r="A211" s="2">
         <v>45501</v>
       </c>
@@ -2157,7 +2169,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="212" spans="1:3">
+    <row r="212" spans="1:3" ht="12.75">
       <c r="A212" s="2">
         <v>45502</v>
       </c>
@@ -2165,7 +2177,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="213" spans="1:3">
+    <row r="213" spans="1:3" ht="12.75">
       <c r="A213" s="2">
         <v>45503</v>
       </c>
@@ -2173,7 +2185,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="214" spans="1:3">
+    <row r="214" spans="1:3" ht="12.75">
       <c r="A214" s="2">
         <v>45504</v>
       </c>
@@ -2181,7 +2193,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="215" spans="1:3">
+    <row r="215" spans="1:3" ht="12.75">
       <c r="A215" s="2">
         <v>45505</v>
       </c>
@@ -2189,7 +2201,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="216" spans="1:3">
+    <row r="216" spans="1:3" ht="12.75">
       <c r="A216" s="2">
         <v>45506</v>
       </c>
@@ -2197,7 +2209,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="217" spans="1:3">
+    <row r="217" spans="1:3" ht="12.75">
       <c r="A217" s="2">
         <v>45507</v>
       </c>
@@ -2205,7 +2217,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="218" spans="1:3">
+    <row r="218" spans="1:3" ht="12.75">
       <c r="A218" s="2">
         <v>45508</v>
       </c>
@@ -2213,7 +2225,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="219" spans="1:3">
+    <row r="219" spans="1:3" ht="12.75">
       <c r="A219" s="2">
         <v>45509</v>
       </c>
@@ -2221,7 +2233,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="220" spans="1:3">
+    <row r="220" spans="1:3" ht="12.75">
       <c r="A220" s="2">
         <v>45510</v>
       </c>
@@ -2229,7 +2241,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="221" spans="1:3">
+    <row r="221" spans="1:3" ht="12.75">
       <c r="A221" s="2">
         <v>45511</v>
       </c>
@@ -2240,7 +2252,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="222" spans="1:3">
+    <row r="222" spans="1:3" ht="12.75">
       <c r="A222" s="2">
         <v>45512</v>
       </c>
@@ -2248,7 +2260,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="223" spans="1:3">
+    <row r="223" spans="1:3" ht="12.75">
       <c r="A223" s="2">
         <v>45513</v>
       </c>
@@ -2256,7 +2268,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="224" spans="1:3">
+    <row r="224" spans="1:3" ht="12.75">
       <c r="A224" s="2">
         <v>45514</v>
       </c>
@@ -2264,7 +2276,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="225" spans="1:3">
+    <row r="225" spans="1:3" ht="12.75">
       <c r="A225" s="2">
         <v>45515</v>
       </c>
@@ -2272,7 +2284,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="226" spans="1:3">
+    <row r="226" spans="1:3" ht="12.75">
       <c r="A226" s="2">
         <v>45516</v>
       </c>
@@ -2283,7 +2295,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="227" spans="1:3">
+    <row r="227" spans="1:3" ht="12.75">
       <c r="A227" s="2">
         <v>45517</v>
       </c>
@@ -2291,7 +2303,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="228" spans="1:3">
+    <row r="228" spans="1:3" ht="12.75">
       <c r="A228" s="2">
         <v>45518</v>
       </c>
@@ -2299,7 +2311,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="229" spans="1:3">
+    <row r="229" spans="1:3" ht="12.75">
       <c r="A229" s="2">
         <v>45519</v>
       </c>
@@ -2310,7 +2322,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="230" spans="1:3">
+    <row r="230" spans="1:3" ht="12.75">
       <c r="A230" s="2">
         <v>45520</v>
       </c>
@@ -2318,7 +2330,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="1:3">
+    <row r="231" spans="1:3" ht="12.75">
       <c r="A231" s="2">
         <v>45521</v>
       </c>
@@ -2326,7 +2338,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="1:3">
+    <row r="232" spans="1:3" ht="12.75">
       <c r="A232" s="2">
         <v>45522</v>
       </c>
@@ -2334,7 +2346,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="233" spans="1:3">
+    <row r="233" spans="1:3" ht="12.75">
       <c r="A233" s="2">
         <v>45523</v>
       </c>
@@ -2342,7 +2354,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="234" spans="1:3">
+    <row r="234" spans="1:3" ht="12.75">
       <c r="A234" s="2">
         <v>45524</v>
       </c>
@@ -2350,7 +2362,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="235" spans="1:3">
+    <row r="235" spans="1:3" ht="12.75">
       <c r="A235" s="2">
         <v>45525</v>
       </c>
@@ -2358,7 +2370,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="236" spans="1:3">
+    <row r="236" spans="1:3" ht="12.75">
       <c r="A236" s="2">
         <v>45526</v>
       </c>
@@ -2366,7 +2378,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="237" spans="1:3">
+    <row r="237" spans="1:3" ht="12.75">
       <c r="A237" s="2">
         <v>45527</v>
       </c>
@@ -2377,7 +2389,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="238" spans="1:3">
+    <row r="238" spans="1:3" ht="12.75">
       <c r="A238" s="2">
         <v>45528</v>
       </c>
@@ -2388,7 +2400,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="239" spans="1:3">
+    <row r="239" spans="1:3" ht="12.75">
       <c r="A239" s="2">
         <v>45529</v>
       </c>
@@ -2396,7 +2408,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="240" spans="1:3">
+    <row r="240" spans="1:3" ht="12.75">
       <c r="A240" s="2">
         <v>45530</v>
       </c>
@@ -2407,7 +2419,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="241" spans="1:2">
+    <row r="241" spans="1:2" ht="12.75">
       <c r="A241" s="2">
         <v>45531</v>
       </c>
@@ -2415,7 +2427,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="242" spans="1:2">
+    <row r="242" spans="1:2" ht="12.75">
       <c r="A242" s="2">
         <v>45532</v>
       </c>
@@ -2423,7 +2435,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="243" spans="1:2">
+    <row r="243" spans="1:2" ht="12.75">
       <c r="A243" s="2">
         <v>45533</v>
       </c>
@@ -2431,7 +2443,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="244" spans="1:2">
+    <row r="244" spans="1:2" ht="12.75">
       <c r="A244" s="2">
         <v>45534</v>
       </c>
@@ -2439,7 +2451,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="245" spans="1:2">
+    <row r="245" spans="1:2" ht="12.75">
       <c r="A245" s="2">
         <v>45535</v>
       </c>
@@ -2447,7 +2459,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="246" spans="1:2">
+    <row r="246" spans="1:2" ht="12.75">
       <c r="A246" s="2">
         <v>45536</v>
       </c>
@@ -2455,7 +2467,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="247" spans="1:2">
+    <row r="247" spans="1:2" ht="12.75">
       <c r="A247" s="2">
         <v>45537</v>
       </c>
@@ -2463,7 +2475,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="248" spans="1:2">
+    <row r="248" spans="1:2" ht="12.75">
       <c r="A248" s="2">
         <v>45538</v>
       </c>
@@ -2471,7 +2483,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="249" spans="1:2">
+    <row r="249" spans="1:2" ht="12.75">
       <c r="A249" s="2">
         <v>45539</v>
       </c>
@@ -2479,7 +2491,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="250" spans="1:2">
+    <row r="250" spans="1:2" ht="12.75">
       <c r="A250" s="2">
         <v>45540</v>
       </c>
@@ -2487,7 +2499,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="251" spans="1:2">
+    <row r="251" spans="1:2" ht="12.75">
       <c r="A251" s="2">
         <v>45541</v>
       </c>
@@ -2495,7 +2507,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="252" spans="1:2">
+    <row r="252" spans="1:2" ht="12.75">
       <c r="A252" s="2">
         <v>45542</v>
       </c>
@@ -2503,7 +2515,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:2">
+    <row r="253" spans="1:2" ht="12.75">
       <c r="A253" s="2">
         <v>45543</v>
       </c>
@@ -2511,7 +2523,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="1:2">
+    <row r="254" spans="1:2" ht="12.75">
       <c r="A254" s="2">
         <v>45544</v>
       </c>
@@ -2519,7 +2531,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="255" spans="1:2">
+    <row r="255" spans="1:2" ht="12.75">
       <c r="A255" s="2">
         <v>45545</v>
       </c>
@@ -2527,7 +2539,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="256" spans="1:2">
+    <row r="256" spans="1:2" ht="12.75">
       <c r="A256" s="2">
         <v>45546</v>
       </c>
@@ -2535,7 +2547,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="257" spans="1:3">
+    <row r="257" spans="1:3" ht="12.75">
       <c r="A257" s="2">
         <v>45547</v>
       </c>
@@ -2543,7 +2555,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="258" spans="1:3">
+    <row r="258" spans="1:3" ht="12.75">
       <c r="A258" s="2">
         <v>45548</v>
       </c>
@@ -2551,7 +2563,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="259" spans="1:3">
+    <row r="259" spans="1:3" ht="12.75">
       <c r="A259" s="2">
         <v>45549</v>
       </c>
@@ -2559,7 +2571,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="260" spans="1:3">
+    <row r="260" spans="1:3" ht="12.75">
       <c r="A260" s="2">
         <v>45550</v>
       </c>
@@ -2567,7 +2579,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="261" spans="1:3">
+    <row r="261" spans="1:3" ht="12.75">
       <c r="A261" s="2">
         <v>45551</v>
       </c>
@@ -2578,7 +2590,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="262" spans="1:3">
+    <row r="262" spans="1:3" ht="12.75">
       <c r="A262" s="2">
         <v>45552</v>
       </c>
@@ -2586,7 +2598,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="263" spans="1:3">
+    <row r="263" spans="1:3" ht="12.75">
       <c r="A263" s="2">
         <v>45553</v>
       </c>
@@ -2594,7 +2606,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="264" spans="1:3">
+    <row r="264" spans="1:3" ht="12.75">
       <c r="A264" s="2">
         <v>45554</v>
       </c>
@@ -2602,7 +2614,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="265" spans="1:3">
+    <row r="265" spans="1:3" ht="12.75">
       <c r="A265" s="2">
         <v>45555</v>
       </c>
@@ -2610,7 +2622,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="266" spans="1:3">
+    <row r="266" spans="1:3" ht="12.75">
       <c r="A266" s="2">
         <v>45556</v>
       </c>
@@ -2618,7 +2630,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="1:3">
+    <row r="267" spans="1:3" ht="12.75">
       <c r="A267" s="2">
         <v>45557</v>
       </c>
@@ -2626,7 +2638,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="268" spans="1:3">
+    <row r="268" spans="1:3" ht="12.75">
       <c r="A268" s="2">
         <v>45558</v>
       </c>
@@ -2634,7 +2646,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="269" spans="1:3">
+    <row r="269" spans="1:3" ht="12.75">
       <c r="A269" s="2">
         <v>45559</v>
       </c>
@@ -2642,7 +2654,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="270" spans="1:3">
+    <row r="270" spans="1:3" ht="12.75">
       <c r="A270" s="2">
         <v>45560</v>
       </c>
@@ -2650,7 +2662,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="271" spans="1:3">
+    <row r="271" spans="1:3" ht="12.75">
       <c r="A271" s="2">
         <v>45561</v>
       </c>
@@ -2658,7 +2670,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="272" spans="1:3">
+    <row r="272" spans="1:3" ht="12.75">
       <c r="A272" s="2">
         <v>45562</v>
       </c>
@@ -2666,7 +2678,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="273" spans="1:3">
+    <row r="273" spans="1:3" ht="12.75">
       <c r="A273" s="2">
         <v>45563</v>
       </c>
@@ -2674,7 +2686,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="274" spans="1:3">
+    <row r="274" spans="1:3" ht="12.75">
       <c r="A274" s="2">
         <v>45564</v>
       </c>
@@ -2682,7 +2694,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="275" spans="1:3">
+    <row r="275" spans="1:3" ht="12.75">
       <c r="A275" s="2">
         <v>45565</v>
       </c>
@@ -2690,7 +2702,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="276" spans="1:3">
+    <row r="276" spans="1:3" ht="12.75">
       <c r="A276" s="2">
         <v>45566</v>
       </c>
@@ -2698,7 +2710,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="277" spans="1:3">
+    <row r="277" spans="1:3" ht="12.75">
       <c r="A277" s="2">
         <v>45567</v>
       </c>
@@ -2709,7 +2721,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="278" spans="1:3">
+    <row r="278" spans="1:3" ht="12.75">
       <c r="A278" s="2">
         <v>45568</v>
       </c>
@@ -2717,7 +2729,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="279" spans="1:3">
+    <row r="279" spans="1:3" ht="12.75">
       <c r="A279" s="2">
         <v>45569</v>
       </c>
@@ -2725,7 +2737,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="280" spans="1:3">
+    <row r="280" spans="1:3" ht="12.75">
       <c r="A280" s="2">
         <v>45570</v>
       </c>
@@ -2733,7 +2745,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="281" spans="1:3">
+    <row r="281" spans="1:3" ht="12.75">
       <c r="A281" s="2">
         <v>45571</v>
       </c>
@@ -2741,7 +2753,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="282" spans="1:3">
+    <row r="282" spans="1:3" ht="12.75">
       <c r="A282" s="2">
         <v>45572</v>
       </c>
@@ -2749,7 +2761,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="283" spans="1:3">
+    <row r="283" spans="1:3" ht="12.75">
       <c r="A283" s="2">
         <v>45573</v>
       </c>
@@ -2757,7 +2769,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="284" spans="1:3">
+    <row r="284" spans="1:3" ht="12.75">
       <c r="A284" s="2">
         <v>45574</v>
       </c>
@@ -2765,7 +2777,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="285" spans="1:3">
+    <row r="285" spans="1:3" ht="12.75">
       <c r="A285" s="2">
         <v>45575</v>
       </c>
@@ -2773,7 +2785,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="286" spans="1:3">
+    <row r="286" spans="1:3" ht="12.75">
       <c r="A286" s="2">
         <v>45576</v>
       </c>
@@ -2781,7 +2793,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="287" spans="1:3">
+    <row r="287" spans="1:3" ht="12.75">
       <c r="A287" s="2">
         <v>45577</v>
       </c>
@@ -2792,7 +2804,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="288" spans="1:3">
+    <row r="288" spans="1:3" ht="12.75">
       <c r="A288" s="2">
         <v>45578</v>
       </c>
@@ -2800,7 +2812,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="289" spans="1:2">
+    <row r="289" spans="1:2" ht="12.75">
       <c r="A289" s="2">
         <v>45579</v>
       </c>
@@ -2808,7 +2820,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="290" spans="1:2">
+    <row r="290" spans="1:2" ht="12.75">
       <c r="A290" s="2">
         <v>45580</v>
       </c>
@@ -2816,7 +2828,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="291" spans="1:2">
+    <row r="291" spans="1:2" ht="12.75">
       <c r="A291" s="2">
         <v>45581</v>
       </c>
@@ -2824,7 +2836,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="292" spans="1:2">
+    <row r="292" spans="1:2" ht="12.75">
       <c r="A292" s="2">
         <v>45582</v>
       </c>
@@ -2832,7 +2844,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="293" spans="1:2">
+    <row r="293" spans="1:2" ht="12.75">
       <c r="A293" s="2">
         <v>45583</v>
       </c>
@@ -2840,7 +2852,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="294" spans="1:2">
+    <row r="294" spans="1:2" ht="12.75">
       <c r="A294" s="2">
         <v>45584</v>
       </c>
@@ -2848,7 +2860,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="295" spans="1:2">
+    <row r="295" spans="1:2" ht="12.75">
       <c r="A295" s="2">
         <v>45585</v>
       </c>
@@ -2856,7 +2868,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="296" spans="1:2">
+    <row r="296" spans="1:2" ht="12.75">
       <c r="A296" s="2">
         <v>45586</v>
       </c>
@@ -2864,7 +2876,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="297" spans="1:2">
+    <row r="297" spans="1:2" ht="12.75">
       <c r="A297" s="2">
         <v>45587</v>
       </c>
@@ -2872,7 +2884,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="298" spans="1:2">
+    <row r="298" spans="1:2" ht="12.75">
       <c r="A298" s="2">
         <v>45588</v>
       </c>
@@ -2880,7 +2892,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="299" spans="1:2">
+    <row r="299" spans="1:2" ht="12.75">
       <c r="A299" s="2">
         <v>45589</v>
       </c>
@@ -2888,7 +2900,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="300" spans="1:2">
+    <row r="300" spans="1:2" ht="12.75">
       <c r="A300" s="2">
         <v>45590</v>
       </c>
@@ -2896,7 +2908,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="301" spans="1:2">
+    <row r="301" spans="1:2" ht="12.75">
       <c r="A301" s="2">
         <v>45591</v>
       </c>
@@ -2904,7 +2916,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="302" spans="1:2">
+    <row r="302" spans="1:2" ht="12.75">
       <c r="A302" s="2">
         <v>45592</v>
       </c>
@@ -2912,7 +2924,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="303" spans="1:2">
+    <row r="303" spans="1:2" ht="12.75">
       <c r="A303" s="2">
         <v>45593</v>
       </c>
@@ -2920,7 +2932,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="304" spans="1:2">
+    <row r="304" spans="1:2" ht="12.75">
       <c r="A304" s="2">
         <v>45594</v>
       </c>
@@ -2928,7 +2940,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="305" spans="1:2">
+    <row r="305" spans="1:2" ht="12.75">
       <c r="A305" s="2">
         <v>45595</v>
       </c>
@@ -2936,7 +2948,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="306" spans="1:2">
+    <row r="306" spans="1:2" ht="12.75">
       <c r="A306" s="2">
         <v>45596</v>
       </c>
@@ -2944,7 +2956,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="307" spans="1:2">
+    <row r="307" spans="1:2" ht="12.75">
       <c r="A307" s="2">
         <v>45597</v>
       </c>
@@ -2952,7 +2964,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="308" spans="1:2">
+    <row r="308" spans="1:2" ht="12.75">
       <c r="A308" s="2">
         <v>45598</v>
       </c>
@@ -2960,7 +2972,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="309" spans="1:2">
+    <row r="309" spans="1:2" ht="12.75">
       <c r="A309" s="2">
         <v>45599</v>
       </c>
@@ -2968,7 +2980,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="310" spans="1:2">
+    <row r="310" spans="1:2" ht="12.75">
       <c r="A310" s="2">
         <v>45600</v>
       </c>
@@ -2976,7 +2988,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="311" spans="1:2">
+    <row r="311" spans="1:2" ht="12.75">
       <c r="A311" s="2">
         <v>45601</v>
       </c>
@@ -2984,7 +2996,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="312" spans="1:2">
+    <row r="312" spans="1:2" ht="12.75">
       <c r="A312" s="2">
         <v>45602</v>
       </c>
@@ -2992,7 +3004,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="313" spans="1:2">
+    <row r="313" spans="1:2" ht="12.75">
       <c r="A313" s="2">
         <v>45603</v>
       </c>
@@ -3000,7 +3012,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="314" spans="1:2">
+    <row r="314" spans="1:2" ht="12.75">
       <c r="A314" s="2">
         <v>45604</v>
       </c>
@@ -3008,7 +3020,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="315" spans="1:2">
+    <row r="315" spans="1:2" ht="12.75">
       <c r="A315" s="2">
         <v>45605</v>
       </c>
@@ -3016,7 +3028,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="316" spans="1:2">
+    <row r="316" spans="1:2" ht="12.75">
       <c r="A316" s="2">
         <v>45606</v>
       </c>
@@ -3024,7 +3036,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="317" spans="1:2">
+    <row r="317" spans="1:2" ht="12.75">
       <c r="A317" s="2">
         <v>45607</v>
       </c>
@@ -3032,7 +3044,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="318" spans="1:2">
+    <row r="318" spans="1:2" ht="12.75">
       <c r="A318" s="2">
         <v>45608</v>
       </c>
@@ -3040,7 +3052,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="319" spans="1:2">
+    <row r="319" spans="1:2" ht="12.75">
       <c r="A319" s="2">
         <v>45609</v>
       </c>
@@ -3048,7 +3060,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="320" spans="1:2">
+    <row r="320" spans="1:2" ht="12.75">
       <c r="A320" s="2">
         <v>45610</v>
       </c>
@@ -3056,7 +3068,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="321" spans="1:3">
+    <row r="321" spans="1:3" ht="12.75">
       <c r="A321" s="2">
         <v>45611</v>
       </c>
@@ -3067,7 +3079,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="322" spans="1:3">
+    <row r="322" spans="1:3" ht="12.75">
       <c r="A322" s="2">
         <v>45612</v>
       </c>
@@ -3075,7 +3087,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="323" spans="1:3">
+    <row r="323" spans="1:3" ht="12.75">
       <c r="A323" s="2">
         <v>45613</v>
       </c>
@@ -3083,7 +3095,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="324" spans="1:3">
+    <row r="324" spans="1:3" ht="12.75">
       <c r="A324" s="2">
         <v>45614</v>
       </c>
@@ -3091,7 +3103,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="325" spans="1:3">
+    <row r="325" spans="1:3" ht="12.75">
       <c r="A325" s="2">
         <v>45615</v>
       </c>
@@ -3099,7 +3111,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="326" spans="1:3">
+    <row r="326" spans="1:3" ht="12.75">
       <c r="A326" s="2">
         <v>45616</v>
       </c>
@@ -3107,7 +3119,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="327" spans="1:3">
+    <row r="327" spans="1:3" ht="12.75">
       <c r="A327" s="2">
         <v>45617</v>
       </c>
@@ -3115,7 +3127,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="328" spans="1:3">
+    <row r="328" spans="1:3" ht="12.75">
       <c r="A328" s="2">
         <v>45618</v>
       </c>
@@ -3123,7 +3135,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="329" spans="1:3">
+    <row r="329" spans="1:3" ht="12.75">
       <c r="A329" s="2">
         <v>45619</v>
       </c>
@@ -3131,7 +3143,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="330" spans="1:3">
+    <row r="330" spans="1:3" ht="12.75">
       <c r="A330" s="2">
         <v>45620</v>
       </c>
@@ -3139,7 +3151,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="331" spans="1:3">
+    <row r="331" spans="1:3" ht="12.75">
       <c r="A331" s="2">
         <v>45621</v>
       </c>
@@ -3147,7 +3159,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="332" spans="1:3">
+    <row r="332" spans="1:3" ht="12.75">
       <c r="A332" s="2">
         <v>45622</v>
       </c>
@@ -3155,7 +3167,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="333" spans="1:3">
+    <row r="333" spans="1:3" ht="12.75">
       <c r="A333" s="2">
         <v>45623</v>
       </c>
@@ -3163,7 +3175,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="334" spans="1:3">
+    <row r="334" spans="1:3" ht="12.75">
       <c r="A334" s="2">
         <v>45624</v>
       </c>
@@ -3171,7 +3183,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="335" spans="1:3">
+    <row r="335" spans="1:3" ht="12.75">
       <c r="A335" s="2">
         <v>45625</v>
       </c>
@@ -3179,7 +3191,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="336" spans="1:3">
+    <row r="336" spans="1:3" ht="12.75">
       <c r="A336" s="2">
         <v>45626</v>
       </c>
@@ -3187,7 +3199,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="337" spans="1:3">
+    <row r="337" spans="1:3" ht="12.75">
       <c r="A337" s="2">
         <v>45627</v>
       </c>
@@ -3195,7 +3207,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="338" spans="1:3">
+    <row r="338" spans="1:3" ht="12.75">
       <c r="A338" s="2">
         <v>45628</v>
       </c>
@@ -3203,7 +3215,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="339" spans="1:3">
+    <row r="339" spans="1:3" ht="12.75">
       <c r="A339" s="2">
         <v>45629</v>
       </c>
@@ -3214,7 +3226,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="340" spans="1:3">
+    <row r="340" spans="1:3" ht="12.75">
       <c r="A340" s="2">
         <v>45630</v>
       </c>
@@ -3222,7 +3234,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="341" spans="1:3">
+    <row r="341" spans="1:3" ht="12.75">
       <c r="A341" s="2">
         <v>45631</v>
       </c>
@@ -3230,7 +3242,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="342" spans="1:3">
+    <row r="342" spans="1:3" ht="12.75">
       <c r="A342" s="2">
         <v>45632</v>
       </c>
@@ -3238,7 +3250,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="343" spans="1:3">
+    <row r="343" spans="1:3" ht="12.75">
       <c r="A343" s="2">
         <v>45633</v>
       </c>
@@ -3246,7 +3258,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="344" spans="1:3">
+    <row r="344" spans="1:3" ht="12.75">
       <c r="A344" s="2">
         <v>45634</v>
       </c>
@@ -3254,7 +3266,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="345" spans="1:3">
+    <row r="345" spans="1:3" ht="12.75">
       <c r="A345" s="2">
         <v>45635</v>
       </c>
@@ -3262,7 +3274,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="346" spans="1:3">
+    <row r="346" spans="1:3" ht="12.75">
       <c r="A346" s="2">
         <v>45636</v>
       </c>
@@ -3270,7 +3282,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="347" spans="1:3">
+    <row r="347" spans="1:3" ht="12.75">
       <c r="A347" s="2">
         <v>45637</v>
       </c>
@@ -3278,7 +3290,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="348" spans="1:3">
+    <row r="348" spans="1:3" ht="12.75">
       <c r="A348" s="2">
         <v>45638</v>
       </c>
@@ -3286,7 +3298,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="349" spans="1:3">
+    <row r="349" spans="1:3" ht="12.75">
       <c r="A349" s="2">
         <v>45639</v>
       </c>
@@ -3294,7 +3306,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="350" spans="1:3">
+    <row r="350" spans="1:3" ht="12.75">
       <c r="A350" s="2">
         <v>45640</v>
       </c>
@@ -3302,7 +3314,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="351" spans="1:3">
+    <row r="351" spans="1:3" ht="12.75">
       <c r="A351" s="2">
         <v>45641</v>
       </c>
@@ -3310,7 +3322,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="352" spans="1:3">
+    <row r="352" spans="1:3" ht="12.75">
       <c r="A352" s="2">
         <v>45642</v>
       </c>
@@ -3318,7 +3330,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="353" spans="1:2">
+    <row r="353" spans="1:2" ht="12.75">
       <c r="A353" s="2">
         <v>45643</v>
       </c>
@@ -3326,7 +3338,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="354" spans="1:2">
+    <row r="354" spans="1:2" ht="12.75">
       <c r="A354" s="2">
         <v>45644</v>
       </c>
@@ -3334,7 +3346,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="355" spans="1:2">
+    <row r="355" spans="1:2" ht="12.75">
       <c r="A355" s="2">
         <v>45645</v>
       </c>
@@ -3342,7 +3354,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="356" spans="1:2">
+    <row r="356" spans="1:2" ht="12.75">
       <c r="A356" s="2">
         <v>45646</v>
       </c>
@@ -3350,7 +3362,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="357" spans="1:2">
+    <row r="357" spans="1:2" ht="12.75">
       <c r="A357" s="2">
         <v>45647</v>
       </c>
@@ -3358,7 +3370,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="358" spans="1:2">
+    <row r="358" spans="1:2" ht="12.75">
       <c r="A358" s="2">
         <v>45648</v>
       </c>
@@ -3366,7 +3378,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="359" spans="1:2">
+    <row r="359" spans="1:2" ht="12.75">
       <c r="A359" s="2">
         <v>45649</v>
       </c>
@@ -3374,7 +3386,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="360" spans="1:2">
+    <row r="360" spans="1:2" ht="12.75">
       <c r="A360" s="2">
         <v>45650</v>
       </c>
@@ -3382,7 +3394,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="361" spans="1:2">
+    <row r="361" spans="1:2" ht="12.75">
       <c r="A361" s="2">
         <v>45651</v>
       </c>
@@ -3390,7 +3402,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="362" spans="1:2">
+    <row r="362" spans="1:2" ht="12.75">
       <c r="A362" s="2">
         <v>45652</v>
       </c>
@@ -3398,7 +3410,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="363" spans="1:2">
+    <row r="363" spans="1:2" ht="12.75">
       <c r="A363" s="2">
         <v>45653</v>
       </c>
@@ -3406,7 +3418,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="364" spans="1:2">
+    <row r="364" spans="1:2" ht="12.75">
       <c r="A364" s="2">
         <v>45654</v>
       </c>
@@ -3414,7 +3426,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="365" spans="1:2">
+    <row r="365" spans="1:2" ht="12.75">
       <c r="A365" s="2">
         <v>45655</v>
       </c>
@@ -3422,7 +3434,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="366" spans="1:2">
+    <row r="366" spans="1:2" ht="12.75">
       <c r="A366" s="2">
         <v>45656</v>
       </c>
@@ -3430,7 +3442,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="367" spans="1:2">
+    <row r="367" spans="1:2" ht="12.75">
       <c r="A367" s="2">
         <v>45657</v>
       </c>
@@ -3438,7 +3450,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="368" spans="1:2">
+    <row r="368" spans="1:2" ht="12.75">
       <c r="A368" s="2">
         <v>45658</v>
       </c>
@@ -3446,7 +3458,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="369" spans="1:2">
+    <row r="369" spans="1:2" ht="12.75">
       <c r="A369" s="2">
         <v>45659</v>
       </c>
@@ -3454,7 +3466,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="370" spans="1:2">
+    <row r="370" spans="1:2" ht="12.75">
       <c r="A370" s="2">
         <v>45660</v>
       </c>
@@ -3462,7 +3474,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="371" spans="1:2">
+    <row r="371" spans="1:2" ht="12.75">
       <c r="A371" s="2">
         <v>45661</v>
       </c>
@@ -3470,7 +3482,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="372" spans="1:2">
+    <row r="372" spans="1:2" ht="12.75">
       <c r="A372" s="2">
         <v>45662</v>
       </c>
@@ -3478,7 +3490,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="373" spans="1:2">
+    <row r="373" spans="1:2" ht="12.75">
       <c r="A373" s="2">
         <v>45663</v>
       </c>
@@ -3486,7 +3498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="374" spans="1:2">
+    <row r="374" spans="1:2" ht="12.75">
       <c r="A374" s="2">
         <v>45664</v>
       </c>
@@ -3494,7 +3506,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="375" spans="1:2">
+    <row r="375" spans="1:2" ht="12.75">
       <c r="A375" s="2">
         <v>45665</v>
       </c>
@@ -3502,7 +3514,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="376" spans="1:2">
+    <row r="376" spans="1:2" ht="12.75">
       <c r="A376" s="2">
         <v>45666</v>
       </c>
@@ -3510,7 +3522,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="377" spans="1:2">
+    <row r="377" spans="1:2" ht="12.75">
       <c r="A377" s="2">
         <v>45667</v>
       </c>
@@ -3518,7 +3530,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="378" spans="1:2">
+    <row r="378" spans="1:2" ht="12.75">
       <c r="A378" s="2">
         <v>45668</v>
       </c>
@@ -3526,7 +3538,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="379" spans="1:2">
+    <row r="379" spans="1:2" ht="12.75">
       <c r="A379" s="2">
         <v>45669</v>
       </c>
@@ -3534,7 +3546,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="380" spans="1:2">
+    <row r="380" spans="1:2" ht="12.75">
       <c r="A380" s="2">
         <v>45670</v>
       </c>
@@ -3542,7 +3554,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="381" spans="1:2">
+    <row r="381" spans="1:2" ht="12.75">
       <c r="A381" s="2">
         <v>45671</v>
       </c>
@@ -3550,7 +3562,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="382" spans="1:2">
+    <row r="382" spans="1:2" ht="12.75">
       <c r="A382" s="2">
         <v>45672</v>
       </c>
@@ -3558,7 +3570,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="383" spans="1:2">
+    <row r="383" spans="1:2" ht="12.75">
       <c r="A383" s="2">
         <v>45673</v>
       </c>
@@ -3566,7 +3578,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="384" spans="1:2">
+    <row r="384" spans="1:2" ht="12.75">
       <c r="A384" s="2">
         <v>45674</v>
       </c>
@@ -3574,7 +3586,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="385" spans="1:2">
+    <row r="385" spans="1:2" ht="12.75">
       <c r="A385" s="2">
         <v>45675</v>
       </c>
@@ -3582,7 +3594,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="386" spans="1:2">
+    <row r="386" spans="1:2" ht="12.75">
       <c r="A386" s="2">
         <v>45676</v>
       </c>
@@ -3590,7 +3602,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="387" spans="1:2">
+    <row r="387" spans="1:2" ht="12.75">
       <c r="A387" s="2">
         <v>45677</v>
       </c>
@@ -3598,7 +3610,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="388" spans="1:2">
+    <row r="388" spans="1:2" ht="12.75">
       <c r="A388" s="2">
         <v>45678</v>
       </c>
@@ -3606,7 +3618,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="389" spans="1:2">
+    <row r="389" spans="1:2" ht="12.75">
       <c r="A389" s="2">
         <v>45679</v>
       </c>
@@ -3614,7 +3626,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="390" spans="1:2">
+    <row r="390" spans="1:2" ht="12.75">
       <c r="A390" s="2">
         <v>45680</v>
       </c>
@@ -3622,7 +3634,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="391" spans="1:2">
+    <row r="391" spans="1:2" ht="12.75">
       <c r="A391" s="2">
         <v>45681</v>
       </c>
@@ -3630,7 +3642,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="392" spans="1:2">
+    <row r="392" spans="1:2" ht="12.75">
       <c r="A392" s="2">
         <v>45682</v>
       </c>
@@ -3638,7 +3650,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="393" spans="1:2">
+    <row r="393" spans="1:2" ht="12.75">
       <c r="A393" s="2">
         <v>45683</v>
       </c>
@@ -3646,7 +3658,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="394" spans="1:2">
+    <row r="394" spans="1:2" ht="12.75">
       <c r="A394" s="2">
         <v>45684</v>
       </c>
@@ -3654,7 +3666,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="395" spans="1:2">
+    <row r="395" spans="1:2" ht="12.75">
       <c r="A395" s="2">
         <v>45685</v>
       </c>
@@ -3662,7 +3674,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="396" spans="1:2">
+    <row r="396" spans="1:2" ht="12.75">
       <c r="A396" s="2">
         <v>45686</v>
       </c>
@@ -3670,7 +3682,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="397" spans="1:2">
+    <row r="397" spans="1:2" ht="12.75">
       <c r="A397" s="2">
         <v>45687</v>
       </c>
@@ -3678,7 +3690,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="398" spans="1:2">
+    <row r="398" spans="1:2" ht="12.75">
       <c r="A398" s="2">
         <v>45688</v>
       </c>
@@ -3686,7 +3698,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="399" spans="1:2">
+    <row r="399" spans="1:2" ht="12.75">
       <c r="A399" s="2">
         <v>45689</v>
       </c>
@@ -3694,7 +3706,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="400" spans="1:2">
+    <row r="400" spans="1:2" ht="12.75">
       <c r="A400" s="2">
         <v>45690</v>
       </c>
@@ -3702,7 +3714,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="401" spans="1:3">
+    <row r="401" spans="1:3" ht="12.75">
       <c r="A401" s="2">
         <v>45691</v>
       </c>
@@ -3710,7 +3722,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="402" spans="1:3">
+    <row r="402" spans="1:3" ht="12.75">
       <c r="A402" s="2">
         <v>45692</v>
       </c>
@@ -3718,7 +3730,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="403" spans="1:3">
+    <row r="403" spans="1:3" ht="12.75">
       <c r="A403" s="2">
         <v>45693</v>
       </c>
@@ -3729,7 +3741,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="404" spans="1:3">
+    <row r="404" spans="1:3" ht="12.75">
       <c r="A404" s="2">
         <v>45694</v>
       </c>
@@ -3737,7 +3749,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="405" spans="1:3">
+    <row r="405" spans="1:3" ht="12.75">
       <c r="A405" s="2">
         <v>45695</v>
       </c>
@@ -3745,7 +3757,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="406" spans="1:3">
+    <row r="406" spans="1:3" ht="12.75">
       <c r="A406" s="2">
         <v>45696</v>
       </c>
@@ -3753,7 +3765,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="407" spans="1:3">
+    <row r="407" spans="1:3" ht="12.75">
       <c r="A407" s="2">
         <v>45697</v>
       </c>
@@ -3761,7 +3773,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="408" spans="1:3">
+    <row r="408" spans="1:3" ht="12.75">
       <c r="A408" s="2">
         <v>45698</v>
       </c>
@@ -3769,7 +3781,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="409" spans="1:3">
+    <row r="409" spans="1:3" ht="12.75">
       <c r="A409" s="2">
         <v>45699</v>
       </c>
@@ -3777,7 +3789,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="410" spans="1:3">
+    <row r="410" spans="1:3" ht="12.75">
       <c r="A410" s="2">
         <v>45700</v>
       </c>
@@ -3788,7 +3800,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="411" spans="1:3">
+    <row r="411" spans="1:3" ht="12.75">
       <c r="A411" s="2">
         <v>45701</v>
       </c>
@@ -3796,7 +3808,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="412" spans="1:3">
+    <row r="412" spans="1:3" ht="12.75">
       <c r="A412" s="2">
         <v>45702</v>
       </c>
@@ -3804,7 +3816,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="413" spans="1:3">
+    <row r="413" spans="1:3" ht="12.75">
       <c r="A413" s="2">
         <v>45703</v>
       </c>
@@ -3812,7 +3824,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="414" spans="1:3">
+    <row r="414" spans="1:3" ht="12.75">
       <c r="A414" s="2">
         <v>45704</v>
       </c>
@@ -3820,7 +3832,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="415" spans="1:3">
+    <row r="415" spans="1:3" ht="12.75">
       <c r="A415" s="2">
         <v>45705</v>
       </c>
@@ -3828,7 +3840,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="416" spans="1:3">
+    <row r="416" spans="1:3" ht="12.75">
       <c r="A416" s="2">
         <v>45706</v>
       </c>
@@ -3836,7 +3848,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="417" spans="1:2">
+    <row r="417" spans="1:2" ht="12.75">
       <c r="A417" s="2">
         <v>45707</v>
       </c>
@@ -3844,7 +3856,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="418" spans="1:2">
+    <row r="418" spans="1:2" ht="12.75">
       <c r="A418" s="2">
         <v>45708</v>
       </c>
@@ -3852,7 +3864,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="419" spans="1:2">
+    <row r="419" spans="1:2" ht="12.75">
       <c r="A419" s="2">
         <v>45709</v>
       </c>
@@ -3860,7 +3872,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="420" spans="1:2">
+    <row r="420" spans="1:2" ht="12.75">
       <c r="A420" s="2">
         <v>45710</v>
       </c>
@@ -3868,7 +3880,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="421" spans="1:2">
+    <row r="421" spans="1:2" ht="12.75">
       <c r="A421" s="2">
         <v>45711</v>
       </c>
@@ -3876,7 +3888,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="422" spans="1:2">
+    <row r="422" spans="1:2" ht="12.75">
       <c r="A422" s="2">
         <v>45712</v>
       </c>
@@ -3884,7 +3896,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="423" spans="1:2">
+    <row r="423" spans="1:2" ht="12.75">
       <c r="A423" s="2">
         <v>45713</v>
       </c>
@@ -3892,7 +3904,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="424" spans="1:2">
+    <row r="424" spans="1:2" ht="12.75">
       <c r="A424" s="2">
         <v>45714</v>
       </c>
@@ -3900,7 +3912,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="425" spans="1:2">
+    <row r="425" spans="1:2" ht="12.75">
       <c r="A425" s="2">
         <v>45715</v>
       </c>
@@ -3908,7 +3920,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="426" spans="1:2">
+    <row r="426" spans="1:2" ht="12.75">
       <c r="A426" s="2">
         <v>45716</v>
       </c>
@@ -3916,7 +3928,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="427" spans="1:2">
+    <row r="427" spans="1:2" ht="12.75">
       <c r="A427" s="2">
         <v>45717</v>
       </c>
@@ -3924,7 +3936,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="428" spans="1:2">
+    <row r="428" spans="1:2" ht="12.75">
       <c r="A428" s="2">
         <v>45718</v>
       </c>
@@ -3932,7 +3944,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="429" spans="1:2">
+    <row r="429" spans="1:2" ht="12.75">
       <c r="A429" s="2">
         <v>45719</v>
       </c>
@@ -3940,7 +3952,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="430" spans="1:2">
+    <row r="430" spans="1:2" ht="12.75">
       <c r="A430" s="2">
         <v>45720</v>
       </c>
@@ -3948,7 +3960,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="431" spans="1:2">
+    <row r="431" spans="1:2" ht="12.75">
       <c r="A431" s="2">
         <v>45721</v>
       </c>
@@ -3956,7 +3968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="432" spans="1:2">
+    <row r="432" spans="1:2" ht="12.75">
       <c r="A432" s="2">
         <v>45722</v>
       </c>
@@ -3964,7 +3976,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="433" spans="1:3">
+    <row r="433" spans="1:3" ht="12.75">
       <c r="A433" s="2">
         <v>45723</v>
       </c>
@@ -3972,7 +3984,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="434" spans="1:3">
+    <row r="434" spans="1:3" ht="12.75">
       <c r="A434" s="2">
         <v>45724</v>
       </c>
@@ -3983,7 +3995,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="435" spans="1:3">
+    <row r="435" spans="1:3" ht="12.75">
       <c r="A435" s="2">
         <v>45725</v>
       </c>
@@ -3994,7 +4006,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="436" spans="1:3">
+    <row r="436" spans="1:3" ht="12.75">
       <c r="A436" s="2">
         <v>45726</v>
       </c>
@@ -4002,7 +4014,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="437" spans="1:3">
+    <row r="437" spans="1:3" ht="12.75">
       <c r="A437" s="2">
         <v>45727</v>
       </c>
@@ -4010,7 +4022,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="438" spans="1:3">
+    <row r="438" spans="1:3" ht="12.75">
       <c r="A438" s="2">
         <v>45728</v>
       </c>
@@ -4018,7 +4030,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="439" spans="1:3">
+    <row r="439" spans="1:3" ht="12.75">
       <c r="A439" s="2">
         <v>45729</v>
       </c>
@@ -4026,7 +4038,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="440" spans="1:3">
+    <row r="440" spans="1:3" ht="12.75">
       <c r="A440" s="2">
         <v>45730</v>
       </c>
@@ -4034,7 +4046,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="441" spans="1:3">
+    <row r="441" spans="1:3" ht="12.75">
       <c r="A441" s="2">
         <v>45731</v>
       </c>
@@ -4042,7 +4054,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="442" spans="1:3">
+    <row r="442" spans="1:3" ht="12.75">
       <c r="A442" s="2">
         <v>45732</v>
       </c>
@@ -4050,7 +4062,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="443" spans="1:3">
+    <row r="443" spans="1:3" ht="12.75">
       <c r="A443" s="2">
         <v>45733</v>
       </c>
@@ -4058,7 +4070,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="444" spans="1:3">
+    <row r="444" spans="1:3" ht="12.75">
       <c r="A444" s="2">
         <v>45734</v>
       </c>
@@ -4066,7 +4078,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="445" spans="1:3">
+    <row r="445" spans="1:3" ht="12.75">
       <c r="A445" s="2">
         <v>45735</v>
       </c>
@@ -4074,7 +4086,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="446" spans="1:3">
+    <row r="446" spans="1:3" ht="12.75">
       <c r="A446" s="2">
         <v>45736</v>
       </c>
@@ -4082,7 +4094,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="447" spans="1:3">
+    <row r="447" spans="1:3" ht="12.75">
       <c r="A447" s="2">
         <v>45737</v>
       </c>
@@ -4093,7 +4105,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="448" spans="1:3">
+    <row r="448" spans="1:3" ht="12.75">
       <c r="A448" s="2">
         <v>45738</v>
       </c>
@@ -4104,7 +4116,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="449" spans="1:3">
+    <row r="449" spans="1:3" ht="12.75">
       <c r="A449" s="2">
         <v>45739</v>
       </c>
@@ -4112,7 +4124,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="450" spans="1:3">
+    <row r="450" spans="1:3" ht="12.75">
       <c r="A450" s="2">
         <v>45740</v>
       </c>
@@ -4120,7 +4132,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="451" spans="1:3">
+    <row r="451" spans="1:3" ht="12.75">
       <c r="A451" s="2">
         <v>45741</v>
       </c>
@@ -4128,7 +4140,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="452" spans="1:3">
+    <row r="452" spans="1:3" ht="12.75">
       <c r="A452" s="2">
         <v>45742</v>
       </c>
@@ -4136,7 +4148,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="453" spans="1:3">
+    <row r="453" spans="1:3" ht="12.75">
       <c r="A453" s="2">
         <v>45743</v>
       </c>
@@ -4144,7 +4156,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="454" spans="1:3">
+    <row r="454" spans="1:3" ht="12.75">
       <c r="A454" s="2">
         <v>45744</v>
       </c>
@@ -4152,7 +4164,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="455" spans="1:3">
+    <row r="455" spans="1:3" ht="12.75">
       <c r="A455" s="2">
         <v>45745</v>
       </c>
@@ -4160,7 +4172,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="456" spans="1:3">
+    <row r="456" spans="1:3" ht="12.75">
       <c r="A456" s="2">
         <v>45746</v>
       </c>
@@ -4168,7 +4180,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="457" spans="1:3">
+    <row r="457" spans="1:3" ht="12.75">
       <c r="A457" s="2">
         <v>45747</v>
       </c>
@@ -4179,7 +4191,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="458" spans="1:3">
+    <row r="458" spans="1:3" ht="12.75">
       <c r="A458" s="2">
         <v>45748</v>
       </c>
@@ -4187,7 +4199,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="459" spans="1:3">
+    <row r="459" spans="1:3" ht="12.75">
       <c r="A459" s="2">
         <v>45749</v>
       </c>
@@ -4195,7 +4207,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="460" spans="1:3">
+    <row r="460" spans="1:3" ht="12.75">
       <c r="A460" s="2">
         <v>45750</v>
       </c>
@@ -4203,7 +4215,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="461" spans="1:3">
+    <row r="461" spans="1:3" ht="12.75">
       <c r="A461" s="2">
         <v>45751</v>
       </c>
@@ -4211,7 +4223,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="462" spans="1:3">
+    <row r="462" spans="1:3" ht="12.75">
       <c r="A462" s="2">
         <v>45752</v>
       </c>
@@ -4219,7 +4231,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="463" spans="1:3">
+    <row r="463" spans="1:3" ht="12.75">
       <c r="A463" s="2">
         <v>45753</v>
       </c>
@@ -4227,7 +4239,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="464" spans="1:3">
+    <row r="464" spans="1:3" ht="12.75">
       <c r="A464" s="2">
         <v>45754</v>
       </c>
@@ -4235,7 +4247,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="465" spans="1:3">
+    <row r="465" spans="1:3" ht="12.75">
       <c r="A465" s="2">
         <v>45755</v>
       </c>
@@ -4243,7 +4255,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="466" spans="1:3">
+    <row r="466" spans="1:3" ht="12.75">
       <c r="A466" s="2">
         <v>45756</v>
       </c>
@@ -4251,7 +4263,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="467" spans="1:3">
+    <row r="467" spans="1:3" ht="12.75">
       <c r="A467" s="2">
         <v>45757</v>
       </c>
@@ -4262,7 +4274,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="468" spans="1:3">
+    <row r="468" spans="1:3" ht="12.75">
       <c r="A468" s="2">
         <v>45758</v>
       </c>
@@ -4270,7 +4282,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="469" spans="1:3">
+    <row r="469" spans="1:3" ht="12.75">
       <c r="A469" s="2">
         <v>45759</v>
       </c>
@@ -4278,7 +4290,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="470" spans="1:3">
+    <row r="470" spans="1:3" ht="12.75">
       <c r="A470" s="2">
         <v>45760</v>
       </c>
@@ -4286,7 +4298,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="471" spans="1:3">
+    <row r="471" spans="1:3" ht="12.75">
       <c r="A471" s="2">
         <v>45761</v>
       </c>
@@ -4294,7 +4306,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="472" spans="1:3">
+    <row r="472" spans="1:3" ht="12.75">
       <c r="A472" s="2">
         <v>45762</v>
       </c>
@@ -4302,7 +4314,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="473" spans="1:3">
+    <row r="473" spans="1:3" ht="12.75">
       <c r="A473" s="2">
         <v>45763</v>
       </c>
@@ -4310,7 +4322,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="474" spans="1:3">
+    <row r="474" spans="1:3" ht="12.75">
       <c r="A474" s="2">
         <v>45764</v>
       </c>
@@ -4318,7 +4330,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="475" spans="1:3">
+    <row r="475" spans="1:3" ht="12.75">
       <c r="A475" s="2">
         <v>45765</v>
       </c>
@@ -4329,7 +4341,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="476" spans="1:3">
+    <row r="476" spans="1:3" ht="12.75">
       <c r="A476" s="2">
         <v>45766</v>
       </c>
@@ -4340,7 +4352,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="477" spans="1:3">
+    <row r="477" spans="1:3" ht="12.75">
       <c r="A477" s="2">
         <v>45767</v>
       </c>
@@ -4351,7 +4363,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="478" spans="1:3">
+    <row r="478" spans="1:3" ht="12.75">
       <c r="A478" s="2">
         <v>45768</v>
       </c>
@@ -4359,7 +4371,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="479" spans="1:3">
+    <row r="479" spans="1:3" ht="12.75">
       <c r="A479" s="2">
         <v>45769</v>
       </c>
@@ -4367,7 +4379,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="480" spans="1:3">
+    <row r="480" spans="1:3" ht="12.75">
       <c r="A480" s="2">
         <v>45770</v>
       </c>
@@ -4375,7 +4387,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="481" spans="1:3">
+    <row r="481" spans="1:3" ht="12.75">
       <c r="A481" s="2">
         <v>45771</v>
       </c>
@@ -4383,7 +4395,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="482" spans="1:3">
+    <row r="482" spans="1:3" ht="12.75">
       <c r="A482" s="2">
         <v>45772</v>
       </c>
@@ -4394,7 +4406,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="483" spans="1:3">
+    <row r="483" spans="1:3" ht="12.75">
       <c r="A483" s="2">
         <v>45773</v>
       </c>
@@ -4402,7 +4414,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="484" spans="1:3">
+    <row r="484" spans="1:3" ht="12.75">
       <c r="A484" s="2">
         <v>45774</v>
       </c>
@@ -4410,7 +4422,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="485" spans="1:3">
+    <row r="485" spans="1:3" ht="12.75">
       <c r="A485" s="2">
         <v>45775</v>
       </c>
@@ -4418,7 +4430,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="486" spans="1:3">
+    <row r="486" spans="1:3" ht="12.75">
       <c r="A486" s="2">
         <v>45776</v>
       </c>
@@ -4426,7 +4438,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="487" spans="1:3">
+    <row r="487" spans="1:3" ht="12.75">
       <c r="A487" s="2">
         <v>45777</v>
       </c>
@@ -4434,7 +4446,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="488" spans="1:3">
+    <row r="488" spans="1:3" ht="12.75">
       <c r="A488" s="2">
         <v>45778</v>
       </c>
@@ -4442,7 +4454,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="489" spans="1:3">
+    <row r="489" spans="1:3" ht="12.75">
       <c r="A489" s="2">
         <v>45779</v>
       </c>
@@ -4450,7 +4462,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="490" spans="1:3">
+    <row r="490" spans="1:3" ht="12.75">
       <c r="A490" s="2">
         <v>45780</v>
       </c>
@@ -4458,7 +4470,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="491" spans="1:3">
+    <row r="491" spans="1:3" ht="12.75">
       <c r="A491" s="2">
         <v>45781</v>
       </c>
@@ -4466,7 +4478,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="492" spans="1:3">
+    <row r="492" spans="1:3" ht="12.75">
       <c r="A492" s="2">
         <v>45782</v>
       </c>
@@ -4474,7 +4486,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="493" spans="1:3">
+    <row r="493" spans="1:3" ht="12.75">
       <c r="A493" s="2">
         <v>45783</v>
       </c>
@@ -4482,7 +4494,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="494" spans="1:3">
+    <row r="494" spans="1:3" ht="12.75">
       <c r="A494" s="2">
         <v>45784</v>
       </c>
@@ -4490,7 +4502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="495" spans="1:3">
+    <row r="495" spans="1:3" ht="12.75">
       <c r="A495" s="2">
         <v>45785</v>
       </c>
@@ -4498,7 +4510,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="496" spans="1:3">
+    <row r="496" spans="1:3" ht="12.75">
       <c r="A496" s="2">
         <v>45786</v>
       </c>
@@ -4506,7 +4518,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="497" spans="1:2">
+    <row r="497" spans="1:2" ht="12.75">
       <c r="A497" s="2">
         <v>45787</v>
       </c>
@@ -4514,7 +4526,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="498" spans="1:2">
+    <row r="498" spans="1:2" ht="12.75">
       <c r="A498" s="2">
         <v>45788</v>
       </c>
@@ -4522,7 +4534,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="499" spans="1:2">
+    <row r="499" spans="1:2" ht="12.75">
       <c r="A499" s="2">
         <v>45789</v>
       </c>
@@ -4530,7 +4542,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="500" spans="1:2">
+    <row r="500" spans="1:2" ht="12.75">
       <c r="A500" s="2">
         <v>45790</v>
       </c>
@@ -4538,7 +4550,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="501" spans="1:2">
+    <row r="501" spans="1:2" ht="12.75">
       <c r="A501" s="2">
         <v>45791</v>
       </c>
@@ -4546,7 +4558,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="502" spans="1:2">
+    <row r="502" spans="1:2" ht="12.75">
       <c r="A502" s="2">
         <v>45792</v>
       </c>
@@ -4554,7 +4566,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="503" spans="1:2">
+    <row r="503" spans="1:2" ht="12.75">
       <c r="A503" s="2">
         <v>45793</v>
       </c>
@@ -4562,7 +4574,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="504" spans="1:2">
+    <row r="504" spans="1:2" ht="12.75">
       <c r="A504" s="2">
         <v>45794</v>
       </c>
@@ -4570,7 +4582,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="505" spans="1:2">
+    <row r="505" spans="1:2" ht="12.75">
       <c r="A505" s="2">
         <v>45795</v>
       </c>
@@ -4578,7 +4590,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="506" spans="1:2">
+    <row r="506" spans="1:2" ht="12.75">
       <c r="A506" s="2">
         <v>45796</v>
       </c>
@@ -4586,7 +4598,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="507" spans="1:2">
+    <row r="507" spans="1:2" ht="12.75">
       <c r="A507" s="2">
         <v>45797</v>
       </c>
@@ -4594,7 +4606,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="508" spans="1:2">
+    <row r="508" spans="1:2" ht="12.75">
       <c r="A508" s="2">
         <v>45798</v>
       </c>
@@ -4602,7 +4614,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="509" spans="1:2">
+    <row r="509" spans="1:2" ht="12.75">
       <c r="A509" s="2">
         <v>45799</v>
       </c>
@@ -4610,7 +4622,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="510" spans="1:2">
+    <row r="510" spans="1:2" ht="12.75">
       <c r="A510" s="2">
         <v>45800</v>
       </c>
@@ -4618,7 +4630,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="511" spans="1:2">
+    <row r="511" spans="1:2" ht="12.75">
       <c r="A511" s="2">
         <v>45801</v>
       </c>
@@ -4626,7 +4638,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="512" spans="1:2">
+    <row r="512" spans="1:2" ht="12.75">
       <c r="A512" s="2">
         <v>45802</v>
       </c>
@@ -4634,7 +4646,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="513" spans="1:2">
+    <row r="513" spans="1:2" ht="12.75">
       <c r="A513" s="2">
         <v>45803</v>
       </c>
@@ -4642,7 +4654,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="514" spans="1:2">
+    <row r="514" spans="1:2" ht="12.75">
       <c r="A514" s="2">
         <v>45804</v>
       </c>
@@ -4650,7 +4662,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="515" spans="1:2">
+    <row r="515" spans="1:2" ht="12.75">
       <c r="A515" s="2">
         <v>45805</v>
       </c>
@@ -4658,7 +4670,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="516" spans="1:2">
+    <row r="516" spans="1:2" ht="12.75">
       <c r="A516" s="2">
         <v>45806</v>
       </c>
@@ -4666,7 +4678,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="517" spans="1:2">
+    <row r="517" spans="1:2" ht="12.75">
       <c r="A517" s="2">
         <v>45807</v>
       </c>
@@ -4674,7 +4686,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="518" spans="1:2">
+    <row r="518" spans="1:2" ht="12.75">
       <c r="A518" s="2">
         <v>45808</v>
       </c>
@@ -4682,7 +4694,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="519" spans="1:2">
+    <row r="519" spans="1:2" ht="12.75">
       <c r="A519" s="2">
         <v>45809</v>
       </c>
@@ -4690,7 +4702,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="520" spans="1:2">
+    <row r="520" spans="1:2" ht="12.75">
       <c r="A520" s="2">
         <v>45810</v>
       </c>
@@ -4698,7 +4710,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="521" spans="1:2">
+    <row r="521" spans="1:2" ht="12.75">
       <c r="A521" s="2">
         <v>45811</v>
       </c>
@@ -4706,7 +4718,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="522" spans="1:2">
+    <row r="522" spans="1:2" ht="12.75">
       <c r="A522" s="2">
         <v>45812</v>
       </c>
@@ -4714,7 +4726,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="523" spans="1:2">
+    <row r="523" spans="1:2" ht="12.75">
       <c r="A523" s="2">
         <v>45813</v>
       </c>
@@ -4722,7 +4734,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="524" spans="1:2">
+    <row r="524" spans="1:2" ht="12.75">
       <c r="A524" s="2">
         <v>45814</v>
       </c>
@@ -4730,7 +4742,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="525" spans="1:2">
+    <row r="525" spans="1:2" ht="12.75">
       <c r="A525" s="2">
         <v>45815</v>
       </c>
@@ -4738,7 +4750,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="526" spans="1:2">
+    <row r="526" spans="1:2" ht="12.75">
       <c r="A526" s="2">
         <v>45816</v>
       </c>
@@ -4746,7 +4758,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="527" spans="1:2">
+    <row r="527" spans="1:2" ht="12.75">
       <c r="A527" s="2">
         <v>45817</v>
       </c>
@@ -4754,7 +4766,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="528" spans="1:2">
+    <row r="528" spans="1:2" ht="12.75">
       <c r="A528" s="2">
         <v>45818</v>
       </c>
@@ -4762,7 +4774,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="529" spans="1:2">
+    <row r="529" spans="1:2" ht="12.75">
       <c r="A529" s="2">
         <v>45819</v>
       </c>
@@ -4770,7 +4782,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="530" spans="1:2">
+    <row r="530" spans="1:2" ht="12.75">
       <c r="A530" s="2">
         <v>45820</v>
       </c>
@@ -4778,7 +4790,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="531" spans="1:2">
+    <row r="531" spans="1:2" ht="12.75">
       <c r="A531" s="2">
         <v>45821</v>
       </c>
@@ -4786,7 +4798,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="532" spans="1:2">
+    <row r="532" spans="1:2" ht="12.75">
       <c r="A532" s="2">
         <v>45822</v>
       </c>
@@ -4794,7 +4806,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="533" spans="1:2">
+    <row r="533" spans="1:2" ht="12.75">
       <c r="A533" s="2">
         <v>45823</v>
       </c>
@@ -4802,7 +4814,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="534" spans="1:2">
+    <row r="534" spans="1:2" ht="12.75">
       <c r="A534" s="2">
         <v>45824</v>
       </c>
@@ -4810,7 +4822,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="535" spans="1:2">
+    <row r="535" spans="1:2" ht="12.75">
       <c r="A535" s="2">
         <v>45825</v>
       </c>
@@ -4818,7 +4830,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="536" spans="1:2">
+    <row r="536" spans="1:2" ht="12.75">
       <c r="A536" s="2">
         <v>45826</v>
       </c>
@@ -4826,7 +4838,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="537" spans="1:2">
+    <row r="537" spans="1:2" ht="12.75">
       <c r="A537" s="2">
         <v>45827</v>
       </c>
@@ -4834,7 +4846,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="538" spans="1:2">
+    <row r="538" spans="1:2" ht="12.75">
       <c r="A538" s="2">
         <v>45828</v>
       </c>
@@ -4842,7 +4854,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="539" spans="1:2">
+    <row r="539" spans="1:2" ht="12.75">
       <c r="A539" s="2">
         <v>45829</v>
       </c>
@@ -4850,7 +4862,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="540" spans="1:2">
+    <row r="540" spans="1:2" ht="12.75">
       <c r="A540" s="2">
         <v>45830</v>
       </c>
@@ -4858,7 +4870,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="541" spans="1:2">
+    <row r="541" spans="1:2" ht="12.75">
       <c r="A541" s="2">
         <v>45831</v>
       </c>
@@ -4866,7 +4878,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="542" spans="1:2">
+    <row r="542" spans="1:2" ht="12.75">
       <c r="A542" s="2">
         <v>45832</v>
       </c>
@@ -4874,7 +4886,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="543" spans="1:2">
+    <row r="543" spans="1:2" ht="12.75">
       <c r="A543" s="2">
         <v>45833</v>
       </c>
@@ -4882,7 +4894,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="544" spans="1:2">
+    <row r="544" spans="1:2" ht="12.75">
       <c r="A544" s="2">
         <v>45834</v>
       </c>
@@ -4890,7 +4902,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="545" spans="1:2">
+    <row r="545" spans="1:2" ht="12.75">
       <c r="A545" s="2">
         <v>45835</v>
       </c>
@@ -4898,7 +4910,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="546" spans="1:2">
+    <row r="546" spans="1:2" ht="12.75">
       <c r="A546" s="2">
         <v>45836</v>
       </c>
@@ -4906,7 +4918,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="547" spans="1:2">
+    <row r="547" spans="1:2" ht="12.75">
       <c r="A547" s="2">
         <v>45837</v>
       </c>
@@ -4914,7 +4926,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="548" spans="1:2">
+    <row r="548" spans="1:2" ht="12.75">
       <c r="A548" s="2">
         <v>45838</v>
       </c>
@@ -4922,7 +4934,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="549" spans="1:2">
+    <row r="549" spans="1:2" ht="12.75">
       <c r="A549" s="2">
         <v>45839</v>
       </c>
@@ -4930,7 +4942,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="550" spans="1:2">
+    <row r="550" spans="1:2" ht="12.75">
       <c r="A550" s="2">
         <v>45840</v>
       </c>
@@ -4938,7 +4950,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="551" spans="1:2">
+    <row r="551" spans="1:2" ht="12.75">
       <c r="A551" s="2">
         <v>45841</v>
       </c>
@@ -4946,7 +4958,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="552" spans="1:2">
+    <row r="552" spans="1:2" ht="12.75">
       <c r="A552" s="2">
         <v>45842</v>
       </c>
@@ -4954,7 +4966,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="553" spans="1:2">
+    <row r="553" spans="1:2" ht="12.75">
       <c r="A553" s="2">
         <v>45843</v>
       </c>
@@ -4962,7 +4974,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="554" spans="1:2">
+    <row r="554" spans="1:2" ht="12.75">
       <c r="A554" s="2">
         <v>45844</v>
       </c>
@@ -4970,7 +4982,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="555" spans="1:2">
+    <row r="555" spans="1:2" ht="12.75">
       <c r="A555" s="2">
         <v>45845</v>
       </c>
@@ -4978,7 +4990,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="556" spans="1:2">
+    <row r="556" spans="1:2" ht="12.75">
       <c r="A556" s="2">
         <v>45846</v>
       </c>
@@ -4986,7 +4998,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="557" spans="1:2">
+    <row r="557" spans="1:2" ht="12.75">
       <c r="A557" s="2">
         <v>45847</v>
       </c>
@@ -4994,7 +5006,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="558" spans="1:2">
+    <row r="558" spans="1:2" ht="12.75">
       <c r="A558" s="2">
         <v>45848</v>
       </c>
@@ -5002,7 +5014,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="559" spans="1:2">
+    <row r="559" spans="1:2" ht="12.75">
       <c r="A559" s="2">
         <v>45849</v>
       </c>
@@ -5010,7 +5022,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="560" spans="1:2">
+    <row r="560" spans="1:2" ht="12.75">
       <c r="A560" s="2">
         <v>45850</v>
       </c>
@@ -5018,7 +5030,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="561" spans="1:2">
+    <row r="561" spans="1:2" ht="12.75">
       <c r="A561" s="2">
         <v>45851</v>
       </c>
@@ -5026,7 +5038,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="562" spans="1:2">
+    <row r="562" spans="1:2" ht="12.75">
       <c r="A562" s="2">
         <v>45852</v>
       </c>
@@ -5034,7 +5046,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="563" spans="1:2">
+    <row r="563" spans="1:2" ht="12.75">
       <c r="A563" s="2">
         <v>45853</v>
       </c>
@@ -5042,7 +5054,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="564" spans="1:2">
+    <row r="564" spans="1:2" ht="12.75">
       <c r="A564" s="2">
         <v>45854</v>
       </c>
@@ -5050,7 +5062,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="565" spans="1:2">
+    <row r="565" spans="1:2" ht="12.75">
       <c r="A565" s="2">
         <v>45855</v>
       </c>
@@ -5058,7 +5070,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="566" spans="1:2">
+    <row r="566" spans="1:2" ht="12.75">
       <c r="A566" s="2">
         <v>45856</v>
       </c>
@@ -5066,7 +5078,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="567" spans="1:2">
+    <row r="567" spans="1:2" ht="12.75">
       <c r="A567" s="2">
         <v>45857</v>
       </c>
@@ -5074,7 +5086,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="568" spans="1:2">
+    <row r="568" spans="1:2" ht="12.75">
       <c r="A568" s="2">
         <v>45858</v>
       </c>
@@ -5082,7 +5094,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="569" spans="1:2">
+    <row r="569" spans="1:2" ht="12.75">
       <c r="A569" s="2">
         <v>45859</v>
       </c>
@@ -5090,7 +5102,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="570" spans="1:2">
+    <row r="570" spans="1:2" ht="12.75">
       <c r="A570" s="2">
         <v>45860</v>
       </c>
@@ -5098,7 +5110,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="571" spans="1:2">
+    <row r="571" spans="1:2" ht="12.75">
       <c r="A571" s="2">
         <v>45861</v>
       </c>
@@ -5106,7 +5118,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="572" spans="1:2">
+    <row r="572" spans="1:2" ht="12.75">
       <c r="A572" s="2">
         <v>45862</v>
       </c>
@@ -5114,7 +5126,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="573" spans="1:2">
+    <row r="573" spans="1:2" ht="12.75">
       <c r="A573" s="2">
         <v>45863</v>
       </c>
@@ -5122,7 +5134,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="574" spans="1:2">
+    <row r="574" spans="1:2" ht="12.75">
       <c r="A574" s="2">
         <v>45864</v>
       </c>
@@ -5130,7 +5142,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="575" spans="1:2">
+    <row r="575" spans="1:2" ht="12.75">
       <c r="A575" s="2">
         <v>45865</v>
       </c>
@@ -5138,7 +5150,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="576" spans="1:2">
+    <row r="576" spans="1:2" ht="12.75">
       <c r="A576" s="2">
         <v>45866</v>
       </c>
@@ -5146,7 +5158,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="577" spans="1:3">
+    <row r="577" spans="1:3" ht="12.75">
       <c r="A577" s="2">
         <v>45867</v>
       </c>
@@ -5154,7 +5166,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="578" spans="1:3">
+    <row r="578" spans="1:3" ht="12.75">
       <c r="A578" s="2">
         <v>45868</v>
       </c>
@@ -5162,7 +5174,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="579" spans="1:3">
+    <row r="579" spans="1:3" ht="12.75">
       <c r="A579" s="2">
         <v>45869</v>
       </c>
@@ -5170,7 +5182,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="580" spans="1:3">
+    <row r="580" spans="1:3" ht="12.75">
       <c r="A580" s="2">
         <v>45870</v>
       </c>
@@ -5178,7 +5190,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="581" spans="1:3">
+    <row r="581" spans="1:3" ht="12.75">
       <c r="A581" s="2">
         <v>45871</v>
       </c>
@@ -5186,7 +5198,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="582" spans="1:3">
+    <row r="582" spans="1:3" ht="12.75">
       <c r="A582" s="2">
         <v>45872</v>
       </c>
@@ -5194,7 +5206,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="583" spans="1:3">
+    <row r="583" spans="1:3" ht="12.75">
       <c r="A583" s="2">
         <v>45873</v>
       </c>
@@ -5202,7 +5214,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="584" spans="1:3">
+    <row r="584" spans="1:3" ht="12.75">
       <c r="A584" s="2">
         <v>45874</v>
       </c>
@@ -5210,7 +5222,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="585" spans="1:3">
+    <row r="585" spans="1:3" ht="12.75">
       <c r="A585" s="2">
         <v>45875</v>
       </c>
@@ -5218,7 +5230,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="586" spans="1:3">
+    <row r="586" spans="1:3" ht="12.75">
       <c r="A586" s="2">
         <v>45876</v>
       </c>
@@ -5226,7 +5238,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="587" spans="1:3">
+    <row r="587" spans="1:3" ht="12.75">
       <c r="A587" s="2">
         <v>45877</v>
       </c>
@@ -5234,7 +5246,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="588" spans="1:3">
+    <row r="588" spans="1:3" ht="12.75">
       <c r="A588" s="2">
         <v>45878</v>
       </c>
@@ -5242,7 +5254,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="589" spans="1:3">
+    <row r="589" spans="1:3" ht="12.75">
       <c r="A589" s="2">
         <v>45879</v>
       </c>
@@ -5250,7 +5262,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="590" spans="1:3">
+    <row r="590" spans="1:3" ht="12.75">
       <c r="A590" s="2">
         <v>45880</v>
       </c>
@@ -5261,7 +5273,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="591" spans="1:3">
+    <row r="591" spans="1:3" ht="12.75">
       <c r="A591" s="2">
         <v>45881</v>
       </c>
@@ -5269,7 +5281,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="592" spans="1:3">
+    <row r="592" spans="1:3" ht="12.75">
       <c r="A592" s="2">
         <v>45882</v>
       </c>
@@ -5277,7 +5289,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="593" spans="1:3">
+    <row r="593" spans="1:3" ht="12.75">
       <c r="A593" s="2">
         <v>45883</v>
       </c>
@@ -5285,7 +5297,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="594" spans="1:3">
+    <row r="594" spans="1:3" ht="12.75">
       <c r="A594" s="2">
         <v>45884</v>
       </c>
@@ -5296,7 +5308,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="595" spans="1:3">
+    <row r="595" spans="1:3" ht="12.75">
       <c r="A595" s="2">
         <v>45885</v>
       </c>
@@ -5304,7 +5316,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="596" spans="1:3">
+    <row r="596" spans="1:3" ht="12.75">
       <c r="A596" s="2">
         <v>45886</v>
       </c>
@@ -5312,7 +5324,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="597" spans="1:3">
+    <row r="597" spans="1:3" ht="12.75">
       <c r="A597" s="2">
         <v>45887</v>
       </c>
@@ -5320,7 +5332,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="598" spans="1:3">
+    <row r="598" spans="1:3" ht="12.75">
       <c r="A598" s="2">
         <v>45888</v>
       </c>
@@ -5328,7 +5340,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="599" spans="1:3">
+    <row r="599" spans="1:3" ht="12.75">
       <c r="A599" s="2">
         <v>45889</v>
       </c>
@@ -5336,7 +5348,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="600" spans="1:3">
+    <row r="600" spans="1:3" ht="12.75">
       <c r="A600" s="2">
         <v>45890</v>
       </c>
@@ -5344,7 +5356,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="601" spans="1:3">
+    <row r="601" spans="1:3" ht="12.75">
       <c r="A601" s="2">
         <v>45891</v>
       </c>
@@ -5352,7 +5364,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="602" spans="1:3">
+    <row r="602" spans="1:3" ht="12.75">
       <c r="A602" s="2">
         <v>45892</v>
       </c>
@@ -5360,7 +5372,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="603" spans="1:3">
+    <row r="603" spans="1:3" ht="12.75">
       <c r="A603" s="2">
         <v>45893</v>
       </c>
@@ -5368,7 +5380,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="604" spans="1:3">
+    <row r="604" spans="1:3" ht="12.75">
       <c r="A604" s="2">
         <v>45894</v>
       </c>
@@ -5376,7 +5388,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="605" spans="1:3">
+    <row r="605" spans="1:3" ht="12.75">
       <c r="A605" s="2">
         <v>45895</v>
       </c>
@@ -5384,7 +5396,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="606" spans="1:3">
+    <row r="606" spans="1:3" ht="12.75">
       <c r="A606" s="2">
         <v>45896</v>
       </c>
@@ -5392,7 +5404,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="607" spans="1:3">
+    <row r="607" spans="1:3" ht="12.75">
       <c r="A607" s="2">
         <v>45897</v>
       </c>
@@ -5400,7 +5412,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="608" spans="1:3">
+    <row r="608" spans="1:3" ht="12.75">
       <c r="A608" s="2">
         <v>45898</v>
       </c>
@@ -5411,7 +5423,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="609" spans="1:3">
+    <row r="609" spans="1:3" ht="12.75">
       <c r="A609" s="2">
         <v>45899</v>
       </c>
@@ -5422,7 +5434,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="610" spans="1:3">
+    <row r="610" spans="1:3" ht="12.75">
       <c r="A610" s="2">
         <v>45900</v>
       </c>
@@ -5430,7 +5442,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="611" spans="1:3">
+    <row r="611" spans="1:3" ht="12.75">
       <c r="A611" s="2">
         <v>45901</v>
       </c>
@@ -5438,7 +5450,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="612" spans="1:3">
+    <row r="612" spans="1:3" ht="12.75">
       <c r="A612" s="2">
         <v>45902</v>
       </c>
@@ -5446,7 +5458,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="613" spans="1:3">
+    <row r="613" spans="1:3" ht="12.75">
       <c r="A613" s="2">
         <v>45903</v>
       </c>
@@ -5454,7 +5466,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="614" spans="1:3">
+    <row r="614" spans="1:3" ht="12.75">
       <c r="A614" s="2">
         <v>45904</v>
       </c>
@@ -5462,7 +5474,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="615" spans="1:3">
+    <row r="615" spans="1:3" ht="12.75">
       <c r="A615" s="2">
         <v>45905</v>
       </c>
@@ -5473,7 +5485,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="616" spans="1:3">
+    <row r="616" spans="1:3" ht="12.75">
       <c r="A616" s="2">
         <v>45906</v>
       </c>
@@ -5481,7 +5493,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="617" spans="1:3">
+    <row r="617" spans="1:3" ht="12.75">
       <c r="A617" s="2">
         <v>45907</v>
       </c>
@@ -5489,7 +5501,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="618" spans="1:3">
+    <row r="618" spans="1:3" ht="12.75">
       <c r="A618" s="2">
         <v>45908</v>
       </c>
@@ -5497,7 +5509,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="619" spans="1:3">
+    <row r="619" spans="1:3" ht="12.75">
       <c r="A619" s="2">
         <v>45909</v>
       </c>
@@ -5505,7 +5517,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="620" spans="1:3">
+    <row r="620" spans="1:3" ht="12.75">
       <c r="A620" s="2">
         <v>45910</v>
       </c>
@@ -5513,7 +5525,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="621" spans="1:3">
+    <row r="621" spans="1:3" ht="12.75">
       <c r="A621" s="2">
         <v>45911</v>
       </c>
@@ -5521,7 +5533,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="622" spans="1:3">
+    <row r="622" spans="1:3" ht="12.75">
       <c r="A622" s="2">
         <v>45912</v>
       </c>
@@ -5529,7 +5541,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="623" spans="1:3">
+    <row r="623" spans="1:3" ht="12.75">
       <c r="A623" s="2">
         <v>45913</v>
       </c>
@@ -5540,7 +5552,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="624" spans="1:3">
+    <row r="624" spans="1:3" ht="12.75">
       <c r="A624" s="2">
         <v>45914</v>
       </c>
@@ -5551,7 +5563,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="625" spans="1:2">
+    <row r="625" spans="1:2" ht="12.75">
       <c r="A625" s="2">
         <v>45915</v>
       </c>
@@ -5559,7 +5571,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="626" spans="1:2">
+    <row r="626" spans="1:2" ht="12.75">
       <c r="A626" s="2">
         <v>45916</v>
       </c>
@@ -5567,7 +5579,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="627" spans="1:2">
+    <row r="627" spans="1:2" ht="12.75">
       <c r="A627" s="2">
         <v>45917</v>
       </c>
@@ -5575,7 +5587,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="628" spans="1:2">
+    <row r="628" spans="1:2" ht="12.75">
       <c r="A628" s="2">
         <v>45918</v>
       </c>
@@ -5583,7 +5595,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="629" spans="1:2">
+    <row r="629" spans="1:2" ht="12.75">
       <c r="A629" s="2">
         <v>45919</v>
       </c>
@@ -5591,7 +5603,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="630" spans="1:2">
+    <row r="630" spans="1:2" ht="12.75">
       <c r="A630" s="2">
         <v>45920</v>
       </c>
@@ -5599,7 +5611,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="631" spans="1:2">
+    <row r="631" spans="1:2" ht="12.75">
       <c r="A631" s="2">
         <v>45921</v>
       </c>
@@ -5607,7 +5619,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="632" spans="1:2">
+    <row r="632" spans="1:2" ht="12.75">
       <c r="A632" s="2">
         <v>45922</v>
       </c>
@@ -5615,7 +5627,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="633" spans="1:2">
+    <row r="633" spans="1:2" ht="12.75">
       <c r="A633" s="2">
         <v>45923</v>
       </c>
@@ -5623,7 +5635,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="634" spans="1:2">
+    <row r="634" spans="1:2" ht="12.75">
       <c r="A634" s="2">
         <v>45924</v>
       </c>
@@ -5631,7 +5643,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="635" spans="1:2">
+    <row r="635" spans="1:2" ht="12.75">
       <c r="A635" s="2">
         <v>45925</v>
       </c>
@@ -5639,7 +5651,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="636" spans="1:2">
+    <row r="636" spans="1:2" ht="12.75">
       <c r="A636" s="2">
         <v>45926</v>
       </c>
@@ -5647,7 +5659,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="637" spans="1:2">
+    <row r="637" spans="1:2" ht="12.75">
       <c r="A637" s="2">
         <v>45927</v>
       </c>
@@ -5655,7 +5667,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="638" spans="1:2">
+    <row r="638" spans="1:2" ht="12.75">
       <c r="A638" s="2">
         <v>45928</v>
       </c>
@@ -5663,7 +5675,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="639" spans="1:2">
+    <row r="639" spans="1:2" ht="12.75">
       <c r="A639" s="2">
         <v>45929</v>
       </c>
@@ -5671,7 +5683,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="640" spans="1:2">
+    <row r="640" spans="1:2" ht="12.75">
       <c r="A640" s="2">
         <v>45930</v>
       </c>
@@ -5679,7 +5691,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="641" spans="1:3">
+    <row r="641" spans="1:3" ht="12.75">
       <c r="A641" s="2">
         <v>45931</v>
       </c>
@@ -5687,7 +5699,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="642" spans="1:3">
+    <row r="642" spans="1:3" ht="12.75">
       <c r="A642" s="2">
         <v>45932</v>
       </c>
@@ -5698,7 +5710,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="643" spans="1:3">
+    <row r="643" spans="1:3" ht="12.75">
       <c r="A643" s="2">
         <v>45933</v>
       </c>
@@ -5706,7 +5718,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="644" spans="1:3">
+    <row r="644" spans="1:3" ht="12.75">
       <c r="A644" s="2">
         <v>45934</v>
       </c>
@@ -5714,7 +5726,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="645" spans="1:3">
+    <row r="645" spans="1:3" ht="12.75">
       <c r="A645" s="2">
         <v>45935</v>
       </c>
@@ -5722,7 +5734,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="646" spans="1:3">
+    <row r="646" spans="1:3" ht="12.75">
       <c r="A646" s="2">
         <v>45936</v>
       </c>
@@ -5730,7 +5742,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="647" spans="1:3">
+    <row r="647" spans="1:3" ht="12.75">
       <c r="A647" s="2">
         <v>45937</v>
       </c>
@@ -5738,7 +5750,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="648" spans="1:3">
+    <row r="648" spans="1:3" ht="12.75">
       <c r="A648" s="2">
         <v>45938</v>
       </c>
@@ -5746,7 +5758,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="649" spans="1:3">
+    <row r="649" spans="1:3" ht="12.75">
       <c r="A649" s="2">
         <v>45939</v>
       </c>
@@ -5754,7 +5766,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="650" spans="1:3">
+    <row r="650" spans="1:3" ht="12.75">
       <c r="A650" s="2">
         <v>45940</v>
       </c>
@@ -5762,7 +5774,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="651" spans="1:3">
+    <row r="651" spans="1:3" ht="12.75">
       <c r="A651" s="2">
         <v>45941</v>
       </c>
@@ -5770,7 +5782,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="652" spans="1:3">
+    <row r="652" spans="1:3" ht="12.75">
       <c r="A652" s="2">
         <v>45942</v>
       </c>
@@ -5778,7 +5790,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="653" spans="1:3">
+    <row r="653" spans="1:3" ht="12.75">
       <c r="A653" s="2">
         <v>45943</v>
       </c>
@@ -5786,7 +5798,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="654" spans="1:3">
+    <row r="654" spans="1:3" ht="12.75">
       <c r="A654" s="2">
         <v>45944</v>
       </c>
@@ -5794,7 +5806,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="655" spans="1:3">
+    <row r="655" spans="1:3" ht="12.75">
       <c r="A655" s="2">
         <v>45945</v>
       </c>
@@ -5802,7 +5814,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="656" spans="1:3">
+    <row r="656" spans="1:3" ht="12.75">
       <c r="A656" s="2">
         <v>45946</v>
       </c>
@@ -5810,7 +5822,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="657" spans="1:2">
+    <row r="657" spans="1:2" ht="12.75">
       <c r="A657" s="2">
         <v>45947</v>
       </c>
@@ -5818,7 +5830,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="658" spans="1:2">
+    <row r="658" spans="1:2" ht="12.75">
       <c r="A658" s="2">
         <v>45948</v>
       </c>
@@ -5826,7 +5838,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="659" spans="1:2">
+    <row r="659" spans="1:2" ht="12.75">
       <c r="A659" s="2">
         <v>45949</v>
       </c>
@@ -5834,7 +5846,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="660" spans="1:2">
+    <row r="660" spans="1:2" ht="12.75">
       <c r="A660" s="2">
         <v>45950</v>
       </c>
@@ -5842,7 +5854,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="661" spans="1:2">
+    <row r="661" spans="1:2" ht="12.75">
       <c r="A661" s="2">
         <v>45951</v>
       </c>
@@ -5850,7 +5862,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="662" spans="1:2">
+    <row r="662" spans="1:2" ht="12.75">
       <c r="A662" s="2">
         <v>45952</v>
       </c>
@@ -5858,7 +5870,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="663" spans="1:2">
+    <row r="663" spans="1:2" ht="12.75">
       <c r="A663" s="2">
         <v>45953</v>
       </c>
@@ -5866,7 +5878,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="664" spans="1:2">
+    <row r="664" spans="1:2" ht="12.75">
       <c r="A664" s="2">
         <v>45954</v>
       </c>
@@ -5874,7 +5886,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="665" spans="1:2">
+    <row r="665" spans="1:2" ht="12.75">
       <c r="A665" s="2">
         <v>45955</v>
       </c>
@@ -5882,7 +5894,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="666" spans="1:2">
+    <row r="666" spans="1:2" ht="12.75">
       <c r="A666" s="2">
         <v>45956</v>
       </c>
@@ -5890,7 +5902,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="667" spans="1:2">
+    <row r="667" spans="1:2" ht="12.75">
       <c r="A667" s="2">
         <v>45957</v>
       </c>
@@ -5898,7 +5910,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="668" spans="1:2">
+    <row r="668" spans="1:2" ht="12.75">
       <c r="A668" s="2">
         <v>45958</v>
       </c>
@@ -5906,7 +5918,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="669" spans="1:2">
+    <row r="669" spans="1:2" ht="12.75">
       <c r="A669" s="2">
         <v>45959</v>
       </c>
@@ -5914,7 +5926,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="670" spans="1:2">
+    <row r="670" spans="1:2" ht="12.75">
       <c r="A670" s="2">
         <v>45960</v>
       </c>
@@ -5922,7 +5934,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="671" spans="1:2">
+    <row r="671" spans="1:2" ht="12.75">
       <c r="A671" s="2">
         <v>45961</v>
       </c>
@@ -5930,7 +5942,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="672" spans="1:2">
+    <row r="672" spans="1:2" ht="12.75">
       <c r="A672" s="2">
         <v>45962</v>
       </c>
@@ -5938,7 +5950,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="673" spans="1:3">
+    <row r="673" spans="1:3" ht="12.75">
       <c r="A673" s="2">
         <v>45963</v>
       </c>
@@ -5946,7 +5958,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="674" spans="1:3">
+    <row r="674" spans="1:3" ht="12.75">
       <c r="A674" s="2">
         <v>45964</v>
       </c>
@@ -5954,7 +5966,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="675" spans="1:3">
+    <row r="675" spans="1:3" ht="12.75">
       <c r="A675" s="2">
         <v>45965</v>
       </c>
@@ -5962,7 +5974,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="676" spans="1:3">
+    <row r="676" spans="1:3" ht="12.75">
       <c r="A676" s="2">
         <v>45966</v>
       </c>
@@ -5973,7 +5985,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="677" spans="1:3">
+    <row r="677" spans="1:3" ht="12.75">
       <c r="A677" s="2">
         <v>45967</v>
       </c>
@@ -5981,7 +5993,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="678" spans="1:3">
+    <row r="678" spans="1:3" ht="12.75">
       <c r="A678" s="2">
         <v>45968</v>
       </c>
@@ -5989,7 +6001,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="679" spans="1:3">
+    <row r="679" spans="1:3" ht="12.75">
       <c r="A679" s="2">
         <v>45969</v>
       </c>
@@ -5997,7 +6009,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="680" spans="1:3">
+    <row r="680" spans="1:3" ht="12.75">
       <c r="A680" s="2">
         <v>45970</v>
       </c>
@@ -6005,7 +6017,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="681" spans="1:3">
+    <row r="681" spans="1:3" ht="12.75">
       <c r="A681" s="2">
         <v>45971</v>
       </c>
@@ -6013,7 +6025,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="682" spans="1:3">
+    <row r="682" spans="1:3" ht="12.75">
       <c r="A682" s="2">
         <v>45972</v>
       </c>
@@ -6021,7 +6033,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="683" spans="1:3">
+    <row r="683" spans="1:3" ht="12.75">
       <c r="A683" s="2">
         <v>45973</v>
       </c>
@@ -6029,7 +6041,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="684" spans="1:3">
+    <row r="684" spans="1:3" ht="12.75">
       <c r="A684" s="2">
         <v>45974</v>
       </c>
@@ -6037,7 +6049,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="685" spans="1:3">
+    <row r="685" spans="1:3" ht="12.75">
       <c r="A685" s="2">
         <v>45975</v>
       </c>
@@ -6045,7 +6057,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="686" spans="1:3">
+    <row r="686" spans="1:3" ht="12.75">
       <c r="A686" s="2">
         <v>45976</v>
       </c>
@@ -6053,7 +6065,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="687" spans="1:3">
+    <row r="687" spans="1:3" ht="12.75">
       <c r="A687" s="2">
         <v>45977</v>
       </c>
@@ -6061,7 +6073,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="688" spans="1:3">
+    <row r="688" spans="1:3" ht="12.75">
       <c r="A688" s="2">
         <v>45978</v>
       </c>
@@ -6069,7 +6081,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="689" spans="1:2">
+    <row r="689" spans="1:2" ht="12.75">
       <c r="A689" s="2">
         <v>45979</v>
       </c>
@@ -6077,7 +6089,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="690" spans="1:2">
+    <row r="690" spans="1:2" ht="12.75">
       <c r="A690" s="2">
         <v>45980</v>
       </c>
@@ -6085,7 +6097,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="691" spans="1:2">
+    <row r="691" spans="1:2" ht="12.75">
       <c r="A691" s="2">
         <v>45981</v>
       </c>
@@ -6093,7 +6105,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="692" spans="1:2">
+    <row r="692" spans="1:2" ht="12.75">
       <c r="A692" s="2">
         <v>45982</v>
       </c>
@@ -6101,7 +6113,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="693" spans="1:2">
+    <row r="693" spans="1:2" ht="12.75">
       <c r="A693" s="2">
         <v>45983</v>
       </c>
@@ -6109,7 +6121,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="694" spans="1:2">
+    <row r="694" spans="1:2" ht="12.75">
       <c r="A694" s="2">
         <v>45984</v>
       </c>
@@ -6117,7 +6129,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="695" spans="1:2">
+    <row r="695" spans="1:2" ht="12.75">
       <c r="A695" s="2">
         <v>45985</v>
       </c>
@@ -6125,7 +6137,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="696" spans="1:2">
+    <row r="696" spans="1:2" ht="12.75">
       <c r="A696" s="2">
         <v>45986</v>
       </c>
@@ -6133,7 +6145,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="697" spans="1:2">
+    <row r="697" spans="1:2" ht="12.75">
       <c r="A697" s="2">
         <v>45987</v>
       </c>
@@ -6141,7 +6153,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="698" spans="1:2">
+    <row r="698" spans="1:2" ht="12.75">
       <c r="A698" s="2">
         <v>45988</v>
       </c>
@@ -6149,7 +6161,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="699" spans="1:2">
+    <row r="699" spans="1:2" ht="12.75">
       <c r="A699" s="2">
         <v>45989</v>
       </c>
@@ -6157,7 +6169,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="700" spans="1:2">
+    <row r="700" spans="1:2" ht="12.75">
       <c r="A700" s="2">
         <v>45990</v>
       </c>
@@ -6165,7 +6177,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="701" spans="1:2">
+    <row r="701" spans="1:2" ht="12.75">
       <c r="A701" s="2">
         <v>45991</v>
       </c>
@@ -6173,7 +6185,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="702" spans="1:2">
+    <row r="702" spans="1:2" ht="12.75">
       <c r="A702" s="2">
         <v>45992</v>
       </c>
@@ -6181,7 +6193,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="703" spans="1:2">
+    <row r="703" spans="1:2" ht="12.75">
       <c r="A703" s="2">
         <v>45993</v>
       </c>
@@ -6189,7 +6201,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="704" spans="1:2">
+    <row r="704" spans="1:2" ht="12.75">
       <c r="A704" s="2">
         <v>45994</v>
       </c>
@@ -6197,7 +6209,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="705" spans="1:2">
+    <row r="705" spans="1:2" ht="12.75">
       <c r="A705" s="2">
         <v>45995</v>
       </c>
@@ -6205,7 +6217,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="706" spans="1:2">
+    <row r="706" spans="1:2" ht="12.75">
       <c r="A706" s="2">
         <v>45996</v>
       </c>
@@ -6213,7 +6225,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="707" spans="1:2">
+    <row r="707" spans="1:2" ht="12.75">
       <c r="A707" s="2">
         <v>45997</v>
       </c>
@@ -6221,7 +6233,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="708" spans="1:2">
+    <row r="708" spans="1:2" ht="12.75">
       <c r="A708" s="2">
         <v>45998</v>
       </c>
@@ -6229,7 +6241,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="709" spans="1:2">
+    <row r="709" spans="1:2" ht="12.75">
       <c r="A709" s="2">
         <v>45999</v>
       </c>
@@ -6237,7 +6249,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="710" spans="1:2">
+    <row r="710" spans="1:2" ht="12.75">
       <c r="A710" s="2">
         <v>46000</v>
       </c>
@@ -6245,7 +6257,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="711" spans="1:2">
+    <row r="711" spans="1:2" ht="12.75">
       <c r="A711" s="2">
         <v>46001</v>
       </c>
@@ -6253,7 +6265,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="712" spans="1:2">
+    <row r="712" spans="1:2" ht="12.75">
       <c r="A712" s="2">
         <v>46002</v>
       </c>
@@ -6261,7 +6273,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="713" spans="1:2">
+    <row r="713" spans="1:2" ht="12.75">
       <c r="A713" s="2">
         <v>46003</v>
       </c>
@@ -6269,7 +6281,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="714" spans="1:2">
+    <row r="714" spans="1:2" ht="12.75">
       <c r="A714" s="2">
         <v>46004</v>
       </c>
@@ -6277,7 +6289,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="715" spans="1:2">
+    <row r="715" spans="1:2" ht="12.75">
       <c r="A715" s="2">
         <v>46005</v>
       </c>
@@ -6285,7 +6297,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="716" spans="1:2">
+    <row r="716" spans="1:2" ht="12.75">
       <c r="A716" s="2">
         <v>46006</v>
       </c>
@@ -6293,7 +6305,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="717" spans="1:2">
+    <row r="717" spans="1:2" ht="12.75">
       <c r="A717" s="2">
         <v>46007</v>
       </c>
@@ -6301,7 +6313,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="718" spans="1:2">
+    <row r="718" spans="1:2" ht="12.75">
       <c r="A718" s="2">
         <v>46008</v>
       </c>
@@ -6309,7 +6321,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="719" spans="1:2">
+    <row r="719" spans="1:2" ht="12.75">
       <c r="A719" s="2">
         <v>46009</v>
       </c>
@@ -6317,7 +6329,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="720" spans="1:2">
+    <row r="720" spans="1:2" ht="12.75">
       <c r="A720" s="2">
         <v>46010</v>
       </c>
@@ -6325,7 +6337,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="721" spans="1:2">
+    <row r="721" spans="1:2" ht="12.75">
       <c r="A721" s="2">
         <v>46011</v>
       </c>
@@ -6333,7 +6345,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="722" spans="1:2">
+    <row r="722" spans="1:2" ht="12.75">
       <c r="A722" s="2">
         <v>46012</v>
       </c>
@@ -6341,7 +6353,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="723" spans="1:2">
+    <row r="723" spans="1:2" ht="12.75">
       <c r="A723" s="2">
         <v>46013</v>
       </c>
@@ -6349,7 +6361,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="724" spans="1:2">
+    <row r="724" spans="1:2" ht="12.75">
       <c r="A724" s="2">
         <v>46014</v>
       </c>
@@ -6357,7 +6369,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="725" spans="1:2">
+    <row r="725" spans="1:2" ht="12.75">
       <c r="A725" s="2">
         <v>46015</v>
       </c>
@@ -6365,7 +6377,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="726" spans="1:2">
+    <row r="726" spans="1:2" ht="12.75">
       <c r="A726" s="2">
         <v>46016</v>
       </c>
@@ -6373,7 +6385,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="727" spans="1:2">
+    <row r="727" spans="1:2" ht="12.75">
       <c r="A727" s="2">
         <v>46017</v>
       </c>
@@ -6381,7 +6393,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="728" spans="1:2">
+    <row r="728" spans="1:2" ht="12.75">
       <c r="A728" s="2">
         <v>46018</v>
       </c>
@@ -6389,7 +6401,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="729" spans="1:2">
+    <row r="729" spans="1:2" ht="12.75">
       <c r="A729" s="2">
         <v>46019</v>
       </c>
@@ -6397,7 +6409,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="730" spans="1:2">
+    <row r="730" spans="1:2" ht="12.75">
       <c r="A730" s="2">
         <v>46020</v>
       </c>
@@ -6405,7 +6417,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="731" spans="1:2">
+    <row r="731" spans="1:2" ht="12.75">
       <c r="A731" s="2">
         <v>46021</v>
       </c>
@@ -6413,7 +6425,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="732" spans="1:2">
+    <row r="732" spans="1:2" ht="12.75">
       <c r="A732" s="2">
         <v>46022</v>
       </c>
@@ -7626,7 +7638,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="881" spans="1:2" ht="15.75" customHeight="1">
+    <row r="881" spans="1:5" ht="15.75" customHeight="1">
       <c r="A881" s="4">
         <v>46171</v>
       </c>
@@ -7634,7 +7646,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="882" spans="1:2" ht="15.75" customHeight="1">
+    <row r="882" spans="1:5" ht="15.75" customHeight="1">
       <c r="A882" s="4">
         <v>46172</v>
       </c>
@@ -7642,13 +7654,1402 @@
         <v>18</v>
       </c>
     </row>
-    <row r="883" spans="1:2" ht="15.75" customHeight="1">
+    <row r="883" spans="1:5" ht="15.75" customHeight="1">
       <c r="A883" s="4">
         <v>46173</v>
       </c>
       <c r="B883" s="3" t="s">
         <v>18</v>
       </c>
+    </row>
+    <row r="884" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A884" s="7">
+        <v>46235</v>
+      </c>
+      <c r="B884" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E884" s="6"/>
+    </row>
+    <row r="885" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A885" s="7">
+        <v>46236</v>
+      </c>
+      <c r="B885" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E885" s="6"/>
+    </row>
+    <row r="886" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A886" s="7">
+        <v>46237</v>
+      </c>
+      <c r="B886" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E886" s="6"/>
+    </row>
+    <row r="887" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A887" s="7">
+        <v>46238</v>
+      </c>
+      <c r="B887" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E887" s="6"/>
+    </row>
+    <row r="888" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A888" s="7">
+        <v>46239</v>
+      </c>
+      <c r="B888" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E888" s="6"/>
+    </row>
+    <row r="889" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A889" s="7">
+        <v>46240</v>
+      </c>
+      <c r="B889" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E889" s="6"/>
+    </row>
+    <row r="890" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A890" s="7">
+        <v>46241</v>
+      </c>
+      <c r="B890" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E890" s="6"/>
+    </row>
+    <row r="891" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A891" s="7">
+        <v>46242</v>
+      </c>
+      <c r="B891" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E891" s="6"/>
+    </row>
+    <row r="892" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A892" s="7">
+        <v>46243</v>
+      </c>
+      <c r="B892" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E892" s="6"/>
+    </row>
+    <row r="893" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A893" s="7">
+        <v>46244</v>
+      </c>
+      <c r="B893" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C893" t="s">
+        <v>4</v>
+      </c>
+      <c r="E893" s="6"/>
+    </row>
+    <row r="894" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A894" s="7">
+        <v>46245</v>
+      </c>
+      <c r="B894" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E894" s="6"/>
+    </row>
+    <row r="895" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A895" s="7">
+        <v>46246</v>
+      </c>
+      <c r="B895" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E895" s="6"/>
+    </row>
+    <row r="896" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A896" s="7">
+        <v>46247</v>
+      </c>
+      <c r="B896" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E896" s="6"/>
+    </row>
+    <row r="897" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A897" s="7">
+        <v>46248</v>
+      </c>
+      <c r="B897" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E897" s="6"/>
+    </row>
+    <row r="898" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A898" s="7">
+        <v>46249</v>
+      </c>
+      <c r="B898" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E898" s="6"/>
+    </row>
+    <row r="899" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A899" s="7">
+        <v>46250</v>
+      </c>
+      <c r="B899" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E899" s="6"/>
+    </row>
+    <row r="900" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A900" s="7">
+        <v>46251</v>
+      </c>
+      <c r="B900" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E900" s="6"/>
+    </row>
+    <row r="901" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A901" s="7">
+        <v>46252</v>
+      </c>
+      <c r="B901" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E901" s="6"/>
+    </row>
+    <row r="902" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A902" s="7">
+        <v>46253</v>
+      </c>
+      <c r="B902" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E902" s="6"/>
+    </row>
+    <row r="903" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A903" s="7">
+        <v>46254</v>
+      </c>
+      <c r="B903" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E903" s="6"/>
+    </row>
+    <row r="904" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A904" s="7">
+        <v>46255</v>
+      </c>
+      <c r="B904" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E904" s="6"/>
+    </row>
+    <row r="905" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A905" s="7">
+        <v>46256</v>
+      </c>
+      <c r="B905" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E905" s="6"/>
+    </row>
+    <row r="906" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A906" s="7">
+        <v>46257</v>
+      </c>
+      <c r="B906" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E906" s="6"/>
+    </row>
+    <row r="907" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A907" s="7">
+        <v>46258</v>
+      </c>
+      <c r="B907" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E907" s="6"/>
+    </row>
+    <row r="908" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A908" s="7">
+        <v>46259</v>
+      </c>
+      <c r="B908" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E908" s="6"/>
+    </row>
+    <row r="909" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A909" s="7">
+        <v>46260</v>
+      </c>
+      <c r="B909" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C909" t="s">
+        <v>41</v>
+      </c>
+      <c r="E909" s="6"/>
+    </row>
+    <row r="910" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A910" s="7">
+        <v>46261</v>
+      </c>
+      <c r="B910" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E910" s="6"/>
+    </row>
+    <row r="911" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A911" s="7">
+        <v>46262</v>
+      </c>
+      <c r="B911" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E911" s="6"/>
+    </row>
+    <row r="912" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A912" s="7">
+        <v>46263</v>
+      </c>
+      <c r="B912" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E912" s="6"/>
+    </row>
+    <row r="913" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A913" s="7">
+        <v>46264</v>
+      </c>
+      <c r="B913" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E913" s="6"/>
+    </row>
+    <row r="914" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A914" s="7">
+        <v>46265</v>
+      </c>
+      <c r="B914" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E914" s="6"/>
+    </row>
+    <row r="915" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A915" s="7">
+        <v>46266</v>
+      </c>
+      <c r="B915" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E915" s="6"/>
+    </row>
+    <row r="916" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A916" s="7">
+        <v>46267</v>
+      </c>
+      <c r="B916" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E916" s="6"/>
+    </row>
+    <row r="917" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A917" s="7">
+        <v>46268</v>
+      </c>
+      <c r="B917" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E917" s="6"/>
+    </row>
+    <row r="918" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A918" s="7">
+        <v>46269</v>
+      </c>
+      <c r="B918" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E918" s="6"/>
+    </row>
+    <row r="919" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A919" s="7">
+        <v>46270</v>
+      </c>
+      <c r="B919" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E919" s="6"/>
+    </row>
+    <row r="920" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A920" s="7">
+        <v>46271</v>
+      </c>
+      <c r="B920" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E920" s="6"/>
+    </row>
+    <row r="921" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A921" s="7">
+        <v>46272</v>
+      </c>
+      <c r="B921" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E921" s="6"/>
+    </row>
+    <row r="922" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A922" s="7">
+        <v>46273</v>
+      </c>
+      <c r="B922" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E922" s="6"/>
+    </row>
+    <row r="923" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A923" s="7">
+        <v>46274</v>
+      </c>
+      <c r="B923" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E923" s="6"/>
+    </row>
+    <row r="924" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A924" s="7">
+        <v>46275</v>
+      </c>
+      <c r="B924" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E924" s="6"/>
+    </row>
+    <row r="925" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A925" s="7">
+        <v>46276</v>
+      </c>
+      <c r="B925" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E925" s="6"/>
+    </row>
+    <row r="926" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A926" s="7">
+        <v>46277</v>
+      </c>
+      <c r="B926" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E926" s="6"/>
+    </row>
+    <row r="927" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A927" s="7">
+        <v>46278</v>
+      </c>
+      <c r="B927" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E927" s="6"/>
+    </row>
+    <row r="928" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A928" s="7">
+        <v>46279</v>
+      </c>
+      <c r="B928" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E928" s="6"/>
+    </row>
+    <row r="929" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A929" s="7">
+        <v>46280</v>
+      </c>
+      <c r="B929" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E929" s="6"/>
+    </row>
+    <row r="930" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A930" s="7">
+        <v>46281</v>
+      </c>
+      <c r="B930" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E930" s="6"/>
+    </row>
+    <row r="931" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A931" s="7">
+        <v>46282</v>
+      </c>
+      <c r="B931" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E931" s="6"/>
+    </row>
+    <row r="932" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A932" s="7">
+        <v>46283</v>
+      </c>
+      <c r="B932" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E932" s="6"/>
+    </row>
+    <row r="933" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A933" s="7">
+        <v>46284</v>
+      </c>
+      <c r="B933" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E933" s="6"/>
+    </row>
+    <row r="934" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A934" s="7">
+        <v>46285</v>
+      </c>
+      <c r="B934" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E934" s="6"/>
+    </row>
+    <row r="935" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A935" s="7">
+        <v>46286</v>
+      </c>
+      <c r="B935" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E935" s="6"/>
+    </row>
+    <row r="936" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A936" s="7">
+        <v>46287</v>
+      </c>
+      <c r="B936" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E936" s="6"/>
+    </row>
+    <row r="937" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A937" s="7">
+        <v>46288</v>
+      </c>
+      <c r="B937" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E937" s="6"/>
+    </row>
+    <row r="938" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A938" s="7">
+        <v>46289</v>
+      </c>
+      <c r="B938" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E938" s="6"/>
+    </row>
+    <row r="939" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A939" s="7">
+        <v>46290</v>
+      </c>
+      <c r="B939" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E939" s="6"/>
+    </row>
+    <row r="940" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A940" s="7">
+        <v>46291</v>
+      </c>
+      <c r="B940" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E940" s="6"/>
+    </row>
+    <row r="941" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A941" s="7">
+        <v>46292</v>
+      </c>
+      <c r="B941" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E941" s="6"/>
+    </row>
+    <row r="942" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A942" s="7">
+        <v>46293</v>
+      </c>
+      <c r="B942" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E942" s="6"/>
+    </row>
+    <row r="943" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A943" s="7">
+        <v>46294</v>
+      </c>
+      <c r="B943" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E943" s="6"/>
+    </row>
+    <row r="944" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A944" s="7">
+        <v>46295</v>
+      </c>
+      <c r="B944" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E944" s="6"/>
+    </row>
+    <row r="945" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A945" s="7">
+        <v>46296</v>
+      </c>
+      <c r="B945" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E945" s="6"/>
+    </row>
+    <row r="946" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A946" s="7">
+        <v>46297</v>
+      </c>
+      <c r="B946" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E946" s="6"/>
+    </row>
+    <row r="947" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A947" s="7">
+        <v>46298</v>
+      </c>
+      <c r="B947" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E947" s="6"/>
+    </row>
+    <row r="948" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A948" s="7">
+        <v>46299</v>
+      </c>
+      <c r="B948" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E948" s="6"/>
+    </row>
+    <row r="949" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A949" s="7">
+        <v>46300</v>
+      </c>
+      <c r="B949" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E949" s="6"/>
+    </row>
+    <row r="950" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A950" s="7">
+        <v>46301</v>
+      </c>
+      <c r="B950" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E950" s="6"/>
+    </row>
+    <row r="951" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A951" s="7">
+        <v>46302</v>
+      </c>
+      <c r="B951" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E951" s="6"/>
+    </row>
+    <row r="952" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A952" s="7">
+        <v>46303</v>
+      </c>
+      <c r="B952" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E952" s="6"/>
+    </row>
+    <row r="953" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A953" s="7">
+        <v>46304</v>
+      </c>
+      <c r="B953" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E953" s="6"/>
+    </row>
+    <row r="954" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A954" s="7">
+        <v>46305</v>
+      </c>
+      <c r="B954" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E954" s="6"/>
+    </row>
+    <row r="955" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A955" s="7">
+        <v>46306</v>
+      </c>
+      <c r="B955" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E955" s="6"/>
+    </row>
+    <row r="956" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A956" s="7">
+        <v>46307</v>
+      </c>
+      <c r="B956" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E956" s="6"/>
+    </row>
+    <row r="957" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A957" s="7">
+        <v>46308</v>
+      </c>
+      <c r="B957" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E957" s="6"/>
+    </row>
+    <row r="958" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A958" s="7">
+        <v>46309</v>
+      </c>
+      <c r="B958" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E958" s="6"/>
+    </row>
+    <row r="959" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A959" s="7">
+        <v>46310</v>
+      </c>
+      <c r="B959" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E959" s="6"/>
+    </row>
+    <row r="960" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A960" s="7">
+        <v>46311</v>
+      </c>
+      <c r="B960" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E960" s="6"/>
+    </row>
+    <row r="961" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A961" s="7">
+        <v>46312</v>
+      </c>
+      <c r="B961" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E961" s="6"/>
+    </row>
+    <row r="962" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A962" s="7">
+        <v>46313</v>
+      </c>
+      <c r="B962" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E962" s="6"/>
+    </row>
+    <row r="963" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A963" s="7">
+        <v>46314</v>
+      </c>
+      <c r="B963" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E963" s="6"/>
+    </row>
+    <row r="964" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A964" s="7">
+        <v>46315</v>
+      </c>
+      <c r="B964" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C964" t="s">
+        <v>42</v>
+      </c>
+      <c r="E964" s="6"/>
+    </row>
+    <row r="965" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A965" s="7">
+        <v>46316</v>
+      </c>
+      <c r="B965" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E965" s="6"/>
+    </row>
+    <row r="966" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A966" s="7">
+        <v>46317</v>
+      </c>
+      <c r="B966" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E966" s="6"/>
+    </row>
+    <row r="967" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A967" s="7">
+        <v>46318</v>
+      </c>
+      <c r="B967" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E967" s="6"/>
+    </row>
+    <row r="968" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A968" s="7">
+        <v>46319</v>
+      </c>
+      <c r="B968" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E968" s="6"/>
+    </row>
+    <row r="969" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A969" s="7">
+        <v>46320</v>
+      </c>
+      <c r="B969" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E969" s="6"/>
+    </row>
+    <row r="970" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A970" s="7">
+        <v>46321</v>
+      </c>
+      <c r="B970" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C970" t="s">
+        <v>43</v>
+      </c>
+      <c r="E970" s="6"/>
+    </row>
+    <row r="971" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A971" s="7">
+        <v>46322</v>
+      </c>
+      <c r="B971" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E971" s="6"/>
+    </row>
+    <row r="972" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A972" s="7">
+        <v>46323</v>
+      </c>
+      <c r="B972" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E972" s="6"/>
+    </row>
+    <row r="973" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A973" s="7">
+        <v>46324</v>
+      </c>
+      <c r="B973" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E973" s="6"/>
+    </row>
+    <row r="974" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A974" s="7">
+        <v>46325</v>
+      </c>
+      <c r="B974" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E974" s="6"/>
+    </row>
+    <row r="975" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A975" s="7">
+        <v>46326</v>
+      </c>
+      <c r="B975" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E975" s="6"/>
+    </row>
+    <row r="976" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A976" s="7">
+        <v>46327</v>
+      </c>
+      <c r="B976" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E976" s="6"/>
+    </row>
+    <row r="977" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A977" s="7">
+        <v>46328</v>
+      </c>
+      <c r="B977" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E977" s="6"/>
+    </row>
+    <row r="978" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A978" s="7">
+        <v>46329</v>
+      </c>
+      <c r="B978" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E978" s="6"/>
+    </row>
+    <row r="979" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A979" s="7">
+        <v>46330</v>
+      </c>
+      <c r="B979" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E979" s="6"/>
+    </row>
+    <row r="980" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A980" s="7">
+        <v>46331</v>
+      </c>
+      <c r="B980" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E980" s="6"/>
+    </row>
+    <row r="981" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A981" s="7">
+        <v>46332</v>
+      </c>
+      <c r="B981" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E981" s="6"/>
+    </row>
+    <row r="982" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A982" s="7">
+        <v>46333</v>
+      </c>
+      <c r="B982" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E982" s="6"/>
+    </row>
+    <row r="983" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A983" s="7">
+        <v>46334</v>
+      </c>
+      <c r="B983" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E983" s="6"/>
+    </row>
+    <row r="984" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A984" s="7">
+        <v>46335</v>
+      </c>
+      <c r="B984" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E984" s="6"/>
+    </row>
+    <row r="985" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A985" s="7">
+        <v>46336</v>
+      </c>
+      <c r="B985" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E985" s="6"/>
+    </row>
+    <row r="986" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A986" s="7">
+        <v>46337</v>
+      </c>
+      <c r="B986" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E986" s="6"/>
+    </row>
+    <row r="987" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A987" s="7">
+        <v>46338</v>
+      </c>
+      <c r="B987" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E987" s="6"/>
+    </row>
+    <row r="988" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A988" s="7">
+        <v>46339</v>
+      </c>
+      <c r="B988" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E988" s="6"/>
+    </row>
+    <row r="989" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A989" s="7">
+        <v>46340</v>
+      </c>
+      <c r="B989" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E989" s="6"/>
+    </row>
+    <row r="990" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A990" s="7">
+        <v>46341</v>
+      </c>
+      <c r="B990" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E990" s="6"/>
+    </row>
+    <row r="991" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A991" s="7">
+        <v>46342</v>
+      </c>
+      <c r="B991" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E991" s="6"/>
+    </row>
+    <row r="992" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A992" s="7">
+        <v>46343</v>
+      </c>
+      <c r="B992" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E992" s="6"/>
+    </row>
+    <row r="993" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A993" s="7">
+        <v>46344</v>
+      </c>
+      <c r="B993" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E993" s="6"/>
+    </row>
+    <row r="994" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A994" s="7">
+        <v>46345</v>
+      </c>
+      <c r="B994" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E994" s="6"/>
+    </row>
+    <row r="995" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A995" s="7">
+        <v>46346</v>
+      </c>
+      <c r="B995" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E995" s="6"/>
+    </row>
+    <row r="996" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A996" s="7">
+        <v>46347</v>
+      </c>
+      <c r="B996" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E996" s="6"/>
+    </row>
+    <row r="997" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A997" s="7">
+        <v>46348</v>
+      </c>
+      <c r="B997" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E997" s="6"/>
+    </row>
+    <row r="998" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A998" s="7">
+        <v>46349</v>
+      </c>
+      <c r="B998" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E998" s="6"/>
+    </row>
+    <row r="999" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A999" s="7">
+        <v>46350</v>
+      </c>
+      <c r="B999" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E999" s="6"/>
+    </row>
+    <row r="1000" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1000" s="7">
+        <v>46351</v>
+      </c>
+      <c r="B1000" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1000" s="6"/>
+    </row>
+    <row r="1001" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1001" s="7">
+        <v>46352</v>
+      </c>
+      <c r="B1001" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1001" s="6"/>
+    </row>
+    <row r="1002" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1002" s="7">
+        <v>46353</v>
+      </c>
+      <c r="B1002" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1002" s="6"/>
+    </row>
+    <row r="1003" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1003" s="7">
+        <v>46354</v>
+      </c>
+      <c r="B1003" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1003" s="6"/>
+    </row>
+    <row r="1004" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1004" s="7">
+        <v>46355</v>
+      </c>
+      <c r="B1004" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1004" s="6"/>
+    </row>
+    <row r="1005" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1005" s="7">
+        <v>46356</v>
+      </c>
+      <c r="B1005" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1005" s="6"/>
+    </row>
+    <row r="1006" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1006" s="7">
+        <v>46357</v>
+      </c>
+      <c r="B1006" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1006" s="6"/>
+    </row>
+    <row r="1007" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1007" s="7">
+        <v>46358</v>
+      </c>
+      <c r="B1007" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1007" s="6"/>
+    </row>
+    <row r="1008" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1008" s="7">
+        <v>46359</v>
+      </c>
+      <c r="B1008" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1008" s="6"/>
+    </row>
+    <row r="1009" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1009" s="7">
+        <v>46360</v>
+      </c>
+      <c r="B1009" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1009" s="6"/>
+    </row>
+    <row r="1010" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1010" s="7">
+        <v>46361</v>
+      </c>
+      <c r="B1010" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1010" s="6"/>
+    </row>
+    <row r="1011" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1011" s="7">
+        <v>46362</v>
+      </c>
+      <c r="B1011" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1011" s="6"/>
+    </row>
+    <row r="1012" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1012" s="7">
+        <v>46363</v>
+      </c>
+      <c r="B1012" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1012" s="6"/>
+    </row>
+    <row r="1013" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1013" s="7">
+        <v>46364</v>
+      </c>
+      <c r="B1013" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1013" s="6"/>
+    </row>
+    <row r="1014" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1014" s="7">
+        <v>46365</v>
+      </c>
+      <c r="B1014" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1014" s="6"/>
+    </row>
+    <row r="1015" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1015" s="7">
+        <v>46366</v>
+      </c>
+      <c r="B1015" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1015" s="6"/>
+    </row>
+    <row r="1016" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1016" s="7">
+        <v>46367</v>
+      </c>
+      <c r="B1016" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1016" s="6"/>
+    </row>
+    <row r="1017" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1017" s="7">
+        <v>46368</v>
+      </c>
+      <c r="B1017" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1017" s="6"/>
+    </row>
+    <row r="1018" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1018" s="7">
+        <v>46369</v>
+      </c>
+      <c r="B1018" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1018" s="6"/>
+    </row>
+    <row r="1019" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1019" s="7">
+        <v>46370</v>
+      </c>
+      <c r="B1019" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1019" s="6"/>
+    </row>
+    <row r="1020" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1020" s="7">
+        <v>46371</v>
+      </c>
+      <c r="B1020" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1020" s="6"/>
+    </row>
+    <row r="1021" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1021" s="7">
+        <v>46372</v>
+      </c>
+      <c r="B1021" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1021" s="6"/>
+    </row>
+    <row r="1022" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1022" s="7">
+        <v>46373</v>
+      </c>
+      <c r="B1022" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1022" s="6"/>
+    </row>
+    <row r="1023" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1023" s="7">
+        <v>46374</v>
+      </c>
+      <c r="B1023" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1023" s="6"/>
+    </row>
+    <row r="1024" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1024" s="7">
+        <v>46375</v>
+      </c>
+      <c r="B1024" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1024" s="6"/>
+    </row>
+    <row r="1025" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1025" s="7">
+        <v>46376</v>
+      </c>
+      <c r="B1025" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1025" s="6"/>
+    </row>
+    <row r="1026" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1026" s="7">
+        <v>46377</v>
+      </c>
+      <c r="B1026" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1026" s="6"/>
+    </row>
+    <row r="1027" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1027" s="7">
+        <v>46378</v>
+      </c>
+      <c r="B1027" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1027" s="6"/>
+    </row>
+    <row r="1028" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1028" s="7">
+        <v>46379</v>
+      </c>
+      <c r="B1028" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1028" s="6"/>
+    </row>
+    <row r="1029" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1029" s="7">
+        <v>46380</v>
+      </c>
+      <c r="B1029" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1029" s="6"/>
+    </row>
+    <row r="1030" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1030" s="7">
+        <v>46381</v>
+      </c>
+      <c r="B1030" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1030" s="6"/>
+    </row>
+    <row r="1031" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1031" s="7">
+        <v>46382</v>
+      </c>
+      <c r="B1031" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1031" s="6"/>
+    </row>
+    <row r="1032" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1032" s="7">
+        <v>46383</v>
+      </c>
+      <c r="B1032" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1032" s="6"/>
+    </row>
+    <row r="1033" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1033" s="7">
+        <v>46384</v>
+      </c>
+      <c r="B1033" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1033" s="6"/>
+    </row>
+    <row r="1034" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1034" s="7">
+        <v>46385</v>
+      </c>
+      <c r="B1034" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1034" s="6"/>
+    </row>
+    <row r="1035" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1035" s="7">
+        <v>46386</v>
+      </c>
+      <c r="B1035" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1035" s="6"/>
+    </row>
+    <row r="1036" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A1036" s="7">
+        <v>46387</v>
+      </c>
+      <c r="B1036" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1036" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
